--- a/results.xlsx
+++ b/results.xlsx
@@ -2,14 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
-  <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
+  <workbookPr showInkAnnotation="0" hidePivotFieldList="1" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="5740" yWindow="1920" windowWidth="25360" windowHeight="18260" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="15540" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="140000" calcMode="manual" concurrentCalc="0"/>
+  <pivotCaches>
+    <pivotCache cacheId="12" r:id="rId4"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -19,15 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="40">
   <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>Model0</t>
-  </si>
-  <si>
-    <t>Model8</t>
   </si>
   <si>
     <t>Expected</t>
@@ -35,12 +34,123 @@
   <si>
     <t>Actual</t>
   </si>
+  <si>
+    <t>EN - 0 - l2</t>
+  </si>
+  <si>
+    <t>EN - 8 - l2</t>
+  </si>
+  <si>
+    <t>EN - 0 - l1</t>
+  </si>
+  <si>
+    <t>EN - 8 - l1</t>
+  </si>
+  <si>
+    <t>SVR - 8 - l1</t>
+  </si>
+  <si>
+    <t>rounded</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>l2</t>
+  </si>
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>cutoff</t>
+  </si>
+  <si>
+    <t>loss</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>l1</t>
+  </si>
+  <si>
+    <t>SVR</t>
+  </si>
+  <si>
+    <t>Count of score</t>
+  </si>
+  <si>
+    <t>fd_id</t>
+  </si>
+  <si>
+    <t>S128556021</t>
+  </si>
+  <si>
+    <t>S128558921</t>
+  </si>
+  <si>
+    <t>S128560946</t>
+  </si>
+  <si>
+    <t>S128562122</t>
+  </si>
+  <si>
+    <t>S128690094</t>
+  </si>
+  <si>
+    <t>S128690900</t>
+  </si>
+  <si>
+    <t>S128691698</t>
+  </si>
+  <si>
+    <t>S128692562</t>
+  </si>
+  <si>
+    <t>S128693346</t>
+  </si>
+  <si>
+    <t>S129181179</t>
+  </si>
+  <si>
+    <t>S129446269</t>
+  </si>
+  <si>
+    <t>S129446700</t>
+  </si>
+  <si>
+    <t>S129447099</t>
+  </si>
+  <si>
+    <t>S129447368</t>
+  </si>
+  <si>
+    <t>S129447712</t>
+  </si>
+  <si>
+    <t>S129999113</t>
+  </si>
+  <si>
+    <t>S130000006</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -48,16 +158,79 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF999999"/>
+      <name val="Helvetica"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -65,23 +238,1622 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="115">
+    <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="8" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="10" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="12" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="14" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="16" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="18" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="20" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="22" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="24" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="26" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="28" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="30" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="32" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="34" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="36" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="38" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="40" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="44" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="46" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="48" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="50" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="52" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="54" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="56" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="58" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="60" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="62" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="64" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="66" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="68" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="70" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="72" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="74" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="76" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="78" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="80" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="82" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="84" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="86" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="88" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="90" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="92" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="94" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="96" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="98" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="100" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="102" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="104" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="106" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="108" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="110" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="112" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="114" builtinId="9" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="7" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="9" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="11" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="13" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="15" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="17" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="19" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="21" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="23" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="25" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="27" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="29" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="31" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="33" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="35" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="37" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="39" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="41" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="45" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="47" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="49" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="51" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="53" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="55" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="57" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="59" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="61" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="63" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="65" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="67" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="69" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="71" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="73" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="75" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="77" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="79" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="81" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="83" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="85" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="87" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="89" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="91" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="93" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="95" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="97" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="99" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="101" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="103" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="105" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="107" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="109" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="111" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="113" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="118"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="18"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$A$5:$A$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>150.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>160.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>170.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>180.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>190.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>200.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>210.0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>220.0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>230.0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>240.0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>250.0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>260.0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>270.0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>280.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$B$5:$B$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>13.0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="-2090754408"/>
+        <c:axId val="-2133061752"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet5!$V$3:$V$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>150.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>160.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>170.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>180.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>190.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>200.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>210.0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>220.0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>230.0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>240.0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>250.0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>260.0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>270.0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>280.0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet5!$W$3:$W$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>0.00131912664842662</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.00248593068935784</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.00422517514181524</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.00647669721644443</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.00895397033022763</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.0111642842596271</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.0125544964647117</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.0127327112372427</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.0116465061212589</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.00960779231948683</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.00714833229264748</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.00479666111541324</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.00290286285891706</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.00158440855658821</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="-2090080968"/>
+        <c:axId val="-2090397352"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="-2090080968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="-2090397352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="-2090397352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="-2090080968"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="-2133061752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="-2090754408"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="-2090754408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="-2133061752"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="1.0" l="0.75" r="0.75" t="1.0" header="0.5" footer="0.5"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>184150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Jesse Green" refreshedDate="42038.406953587961" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="100">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:F101" sheet="Sheet4"/>
+  </cacheSource>
+  <cacheFields count="6">
+    <cacheField name="date" numFmtId="14">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2014-01-25T00:00:00" maxDate="2015-02-03T00:00:00"/>
+    </cacheField>
+    <cacheField name="score" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="152.30000000000001" maxValue="281.3"/>
+    </cacheField>
+    <cacheField name="model" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="cutoff" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="8"/>
+    </cacheField>
+    <cacheField name="loss" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="rounded" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="150" maxValue="280" count="14">
+        <n v="240"/>
+        <n v="170"/>
+        <n v="220"/>
+        <n v="210"/>
+        <n v="260"/>
+        <n v="230"/>
+        <n v="250"/>
+        <n v="190"/>
+        <n v="280"/>
+        <n v="160"/>
+        <n v="180"/>
+        <n v="270"/>
+        <n v="200"/>
+        <n v="150"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="100">
+  <r>
+    <d v="2015-01-15T00:00:00"/>
+    <n v="235.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-01-16T00:00:00"/>
+    <n v="170.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-01-16T00:00:00"/>
+    <n v="219.7"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-01-17T00:00:00"/>
+    <n v="240.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-01-18T00:00:00"/>
+    <n v="206.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-01-19T00:00:00"/>
+    <n v="256.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="225.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="247.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-01-22T00:00:00"/>
+    <n v="189.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-23T00:00:00"/>
+    <n v="281.3"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="213.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="214.8"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2014-01-28T00:00:00"/>
+    <n v="207.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2014-01-27T00:00:00"/>
+    <n v="162.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="249.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="191.1"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-15T00:00:00"/>
+    <n v="230"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-01-16T00:00:00"/>
+    <n v="172.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-01-16T00:00:00"/>
+    <n v="219.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-01-17T00:00:00"/>
+    <n v="192.3"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-18T00:00:00"/>
+    <n v="206.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-01-19T00:00:00"/>
+    <n v="258.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="226.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="225.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-01-22T00:00:00"/>
+    <n v="177"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-01-23T00:00:00"/>
+    <n v="231.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="194.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="214.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2014-01-28T00:00:00"/>
+    <n v="208.3"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2014-01-27T00:00:00"/>
+    <n v="166.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="270"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="191.1"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-17T00:00:00"/>
+    <n v="192.3"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-18T00:00:00"/>
+    <n v="206.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-01-19T00:00:00"/>
+    <n v="253.8"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="226.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="248.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-01-22T00:00:00"/>
+    <n v="189.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-23T00:00:00"/>
+    <n v="271.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="205.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="213.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2014-01-28T00:00:00"/>
+    <n v="202"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2014-01-27T00:00:00"/>
+    <n v="152.30000000000001"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="249.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="191.1"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-17T00:00:00"/>
+    <n v="192.3"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-18T00:00:00"/>
+    <n v="206.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-01-19T00:00:00"/>
+    <n v="275.2"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="226.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="249.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-01-22T00:00:00"/>
+    <n v="213.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-01-23T00:00:00"/>
+    <n v="252"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="227.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="215.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2014-01-28T00:00:00"/>
+    <n v="213.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2014-01-27T00:00:00"/>
+    <n v="163.30000000000001"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="220.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="191.1"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-18T00:00:00"/>
+    <n v="243.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-01-19T00:00:00"/>
+    <n v="249.7"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="226.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-01-20T00:00:00"/>
+    <n v="240.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-01-22T00:00:00"/>
+    <n v="213.8"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-01-23T00:00:00"/>
+    <n v="243.6"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="173"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2014-01-25T00:00:00"/>
+    <n v="186.6"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2014-01-28T00:00:00"/>
+    <n v="199.6"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2014-01-27T00:00:00"/>
+    <n v="177.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="220.7"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2014-01-26T00:00:00"/>
+    <n v="188.2"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-29T00:00:00"/>
+    <n v="271.10000000000002"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-01-29T00:00:00"/>
+    <n v="271.10000000000002"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-01-29T00:00:00"/>
+    <n v="271.10000000000002"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-01-29T00:00:00"/>
+    <n v="218.7"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-01-29T00:00:00"/>
+    <n v="264.8"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <d v="2015-01-30T00:00:00"/>
+    <n v="173.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-01-30T00:00:00"/>
+    <n v="173.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-01-30T00:00:00"/>
+    <n v="173.7"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-01-30T00:00:00"/>
+    <n v="173.7"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-01-30T00:00:00"/>
+    <n v="173.7"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="191.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="178.6"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="178.7"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="191.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="217.7"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="219.3"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="205.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="185.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="179.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-01-31T00:00:00"/>
+    <n v="212.8"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-01T00:00:00"/>
+    <n v="254.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-01T00:00:00"/>
+    <n v="254.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-01T00:00:00"/>
+    <n v="254.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-01T00:00:00"/>
+    <n v="254.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-01T00:00:00"/>
+    <n v="254.5"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-02T00:00:00"/>
+    <n v="211.6"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-02T00:00:00"/>
+    <n v="215.6"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-02T00:00:00"/>
+    <n v="214.7"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-02T00:00:00"/>
+    <n v="242"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-02T00:00:00"/>
+    <n v="239"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
+  <location ref="A3:B19" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="6">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item x="13"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="7"/>
+        <item x="12"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="15">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of score" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -406,69 +2178,4049 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:E8"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="2" max="2" width="14.1640625" customWidth="1"/>
     <col min="3" max="3" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5" hidden="1"/>
-    <row r="5" spans="1:5" ht="29" customHeight="1">
-      <c r="B5" s="2" t="s">
+    <row r="1" spans="1:12" ht="53" customHeight="1">
+      <c r="B1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="E1" s="23"/>
+      <c r="F1" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" ht="15" customHeight="1">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D2" t="s">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1">
+      <c r="A3" s="1">
+        <v>42019</v>
+      </c>
+      <c r="B3" s="3">
+        <v>222.26</v>
+      </c>
+      <c r="C3" s="3">
+        <v>235.4</v>
+      </c>
+      <c r="D3" s="3">
+        <v>220.3</v>
+      </c>
+      <c r="E3" s="3">
+        <v>230</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="2"/>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1">
+      <c r="A4" s="1">
+        <v>42020</v>
+      </c>
+      <c r="B4" s="3">
+        <v>208.65</v>
+      </c>
+      <c r="C4" s="3">
+        <v>170.9</v>
+      </c>
+      <c r="D4" s="3">
+        <v>206.87</v>
+      </c>
+      <c r="E4" s="3">
+        <v>172.8</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1">
+      <c r="A5" s="1">
+        <v>42020</v>
+      </c>
+      <c r="B5" s="3">
+        <v>221.04</v>
+      </c>
+      <c r="C5" s="3">
+        <v>219.7</v>
+      </c>
+      <c r="D5" s="3">
+        <v>219.74</v>
+      </c>
+      <c r="E5" s="3">
+        <v>219.7</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1">
+      <c r="A6" s="1">
+        <v>42021</v>
+      </c>
+      <c r="B6" s="4">
+        <v>213.77</v>
+      </c>
+      <c r="C6" s="4">
+        <v>240.4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>213.63</v>
+      </c>
+      <c r="E6" s="5">
+        <v>192.3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>214.21</v>
+      </c>
+      <c r="G6" s="5">
+        <v>192.3</v>
+      </c>
+      <c r="H6" s="5">
+        <v>215.82</v>
+      </c>
+      <c r="I6" s="5">
+        <v>192.3</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1">
       <c r="A7" s="1">
+        <v>42022</v>
+      </c>
+      <c r="B7" s="7">
+        <v>209.59</v>
+      </c>
+      <c r="C7" s="7">
+        <v>206.4</v>
+      </c>
+      <c r="D7" s="7">
+        <v>208.72</v>
+      </c>
+      <c r="E7" s="7">
+        <v>206.4</v>
+      </c>
+      <c r="F7" s="7">
+        <v>209.83</v>
+      </c>
+      <c r="G7" s="7">
+        <v>206.4</v>
+      </c>
+      <c r="H7" s="7">
+        <v>209.31</v>
+      </c>
+      <c r="I7" s="7">
+        <v>206.4</v>
+      </c>
+      <c r="J7" s="8">
+        <v>206.45</v>
+      </c>
+      <c r="K7" s="8">
+        <v>243.3</v>
+      </c>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="1">
+        <v>42023</v>
+      </c>
+      <c r="B8" s="7">
+        <v>218.3</v>
+      </c>
+      <c r="C8" s="7">
+        <v>256.2</v>
+      </c>
+      <c r="D8" s="8">
+        <v>216.55</v>
+      </c>
+      <c r="E8" s="8">
+        <v>258.7</v>
+      </c>
+      <c r="F8" s="5">
+        <v>217.97</v>
+      </c>
+      <c r="G8" s="5">
+        <v>253.8</v>
+      </c>
+      <c r="H8" s="4">
+        <v>217.45</v>
+      </c>
+      <c r="I8" s="4">
+        <v>275.2</v>
+      </c>
+      <c r="J8" s="9">
+        <v>214.36</v>
+      </c>
+      <c r="K8" s="9">
+        <v>249.7</v>
+      </c>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="1">
+        <v>42024</v>
+      </c>
+      <c r="B9" s="10">
+        <v>231.67</v>
+      </c>
+      <c r="C9" s="10">
+        <v>225.5</v>
+      </c>
+      <c r="D9" s="11">
+        <v>221.95</v>
+      </c>
+      <c r="E9" s="11">
+        <v>226.9</v>
+      </c>
+      <c r="F9" s="11">
+        <v>232.12</v>
+      </c>
+      <c r="G9" s="11">
+        <v>226.9</v>
+      </c>
+      <c r="H9" s="11">
+        <v>230.82</v>
+      </c>
+      <c r="I9" s="11">
+        <v>226.9</v>
+      </c>
+      <c r="J9" s="11">
+        <v>228.3</v>
+      </c>
+      <c r="K9" s="11">
+        <v>226.9</v>
+      </c>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="1">
+        <v>42024</v>
+      </c>
+      <c r="B10" s="7">
+        <v>219.77</v>
+      </c>
+      <c r="C10" s="7">
+        <v>247.5</v>
+      </c>
+      <c r="D10" s="8">
+        <v>218.66</v>
+      </c>
+      <c r="E10" s="8">
+        <v>225.9</v>
+      </c>
+      <c r="F10" s="5">
+        <v>219.88</v>
+      </c>
+      <c r="G10" s="5">
+        <v>248.4</v>
+      </c>
+      <c r="H10" s="4">
+        <v>221.42</v>
+      </c>
+      <c r="I10" s="4">
+        <v>249.7</v>
+      </c>
+      <c r="J10" s="9">
+        <v>221.09</v>
+      </c>
+      <c r="K10" s="9">
+        <v>240.9</v>
+      </c>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="1">
+        <v>42026</v>
+      </c>
+      <c r="B11" s="13">
+        <v>223.72</v>
+      </c>
+      <c r="C11" s="13">
+        <v>189.9</v>
+      </c>
+      <c r="D11" s="12">
+        <v>224.08</v>
+      </c>
+      <c r="E11" s="12">
+        <v>177</v>
+      </c>
+      <c r="F11" s="13">
+        <v>224.29</v>
+      </c>
+      <c r="G11" s="13">
+        <v>189.9</v>
+      </c>
+      <c r="H11" s="11">
+        <v>226.23</v>
+      </c>
+      <c r="I11" s="11">
+        <v>213.8</v>
+      </c>
+      <c r="J11" s="11">
+        <v>224.41</v>
+      </c>
+      <c r="K11" s="11">
+        <v>213.8</v>
+      </c>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="1">
+        <v>42027</v>
+      </c>
+      <c r="B12" s="14">
+        <v>217.08</v>
+      </c>
+      <c r="C12" s="14">
+        <v>281.3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>218.38</v>
+      </c>
+      <c r="E12" s="2">
+        <v>231.8</v>
+      </c>
+      <c r="F12" s="13">
+        <v>217.73</v>
+      </c>
+      <c r="G12" s="13">
+        <v>271.5</v>
+      </c>
+      <c r="H12" s="15">
+        <v>218.36</v>
+      </c>
+      <c r="I12" s="15">
+        <v>252</v>
+      </c>
+      <c r="J12" s="2">
+        <v>213.53</v>
+      </c>
+      <c r="K12" s="2">
+        <v>243.6</v>
+      </c>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="1">
+        <v>41664</v>
+      </c>
+      <c r="B13" s="14">
+        <v>221.06</v>
+      </c>
+      <c r="C13" s="14">
+        <v>213.4</v>
+      </c>
+      <c r="D13" s="2">
+        <v>222.23</v>
+      </c>
+      <c r="E13" s="2">
+        <v>194.9</v>
+      </c>
+      <c r="F13" s="13">
+        <v>221.33</v>
+      </c>
+      <c r="G13" s="13">
+        <v>205.9</v>
+      </c>
+      <c r="H13" s="14">
+        <v>220.52</v>
+      </c>
+      <c r="I13" s="14">
+        <v>227.9</v>
+      </c>
+      <c r="J13" s="2">
+        <v>217.87</v>
+      </c>
+      <c r="K13" s="2">
+        <v>173</v>
+      </c>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="1">
+        <v>41664</v>
+      </c>
+      <c r="B14" s="14">
+        <v>213.33</v>
+      </c>
+      <c r="C14" s="14">
+        <v>214.8</v>
+      </c>
+      <c r="D14">
+        <v>213.2</v>
+      </c>
+      <c r="E14">
+        <v>214.8</v>
+      </c>
+      <c r="F14" s="13">
+        <v>213.68</v>
+      </c>
+      <c r="G14" s="13">
+        <v>213.5</v>
+      </c>
+      <c r="H14" s="15">
+        <v>214.21</v>
+      </c>
+      <c r="I14" s="15">
+        <v>215.8</v>
+      </c>
+      <c r="J14">
+        <v>212.88</v>
+      </c>
+      <c r="K14">
+        <v>186.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1">
+      <c r="A15" s="1">
+        <v>41667</v>
+      </c>
+      <c r="B15" s="14">
+        <v>222.08</v>
+      </c>
+      <c r="C15" s="14">
+        <v>207.2</v>
+      </c>
+      <c r="D15">
+        <v>220.99</v>
+      </c>
+      <c r="E15">
+        <v>208.3</v>
+      </c>
+      <c r="F15" s="13">
+        <v>223.57</v>
+      </c>
+      <c r="G15" s="13">
+        <v>202</v>
+      </c>
+      <c r="H15" s="14">
+        <v>224.09</v>
+      </c>
+      <c r="I15" s="14">
+        <v>213.8</v>
+      </c>
+      <c r="J15">
+        <v>225.3</v>
+      </c>
+      <c r="K15">
+        <v>199.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="1">
+        <v>41666</v>
+      </c>
+      <c r="B16" s="14">
+        <v>215.25</v>
+      </c>
+      <c r="C16" s="14">
+        <v>162.4</v>
+      </c>
+      <c r="D16">
+        <v>215.11</v>
+      </c>
+      <c r="E16">
+        <v>166.8</v>
+      </c>
+      <c r="F16" s="13">
+        <v>215.53</v>
+      </c>
+      <c r="G16" s="13">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="H16" s="15">
+        <v>214.09</v>
+      </c>
+      <c r="I16" s="15">
+        <v>163.30000000000001</v>
+      </c>
+      <c r="J16">
+        <v>213.46</v>
+      </c>
+      <c r="K16">
+        <v>177.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="1">
+        <v>41665</v>
+      </c>
+      <c r="B17" s="14">
+        <v>197.97</v>
+      </c>
+      <c r="C17" s="14">
+        <v>249.2</v>
+      </c>
+      <c r="D17">
+        <v>194.03</v>
+      </c>
+      <c r="E17">
+        <v>270</v>
+      </c>
+      <c r="F17" s="14">
+        <v>197.97</v>
+      </c>
+      <c r="G17" s="14">
+        <v>249.2</v>
+      </c>
+      <c r="H17">
+        <v>196.54</v>
+      </c>
+      <c r="I17">
+        <v>220.7</v>
+      </c>
+      <c r="J17">
+        <v>196.54</v>
+      </c>
+      <c r="K17">
+        <v>220.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="1">
+        <v>41665</v>
+      </c>
+      <c r="B18" s="14">
+        <v>201.61</v>
+      </c>
+      <c r="C18" s="14">
+        <v>191.1</v>
+      </c>
+      <c r="D18">
+        <v>201.95</v>
+      </c>
+      <c r="E18" s="14">
+        <v>191.1</v>
+      </c>
+      <c r="F18" s="13">
+        <v>201.97</v>
+      </c>
+      <c r="G18" s="14">
+        <v>191.1</v>
+      </c>
+      <c r="H18">
+        <v>203.34</v>
+      </c>
+      <c r="I18" s="14">
+        <v>191.1</v>
+      </c>
+      <c r="J18">
+        <v>201.49</v>
+      </c>
+      <c r="K18">
+        <v>188.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="B30">
+        <f>AVERAGE(B3:B18)</f>
+        <v>216.07187499999998</v>
+      </c>
+      <c r="C30">
+        <f>AVERAGE(C3:C18)</f>
+        <v>219.45625000000001</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ref="D30:K30" si="0">AVERAGE(D3:D13)</f>
+        <v>217.37363636363636</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>212.4</v>
+      </c>
+      <c r="F30">
+        <f>AVERAGE(F3:F16)</f>
+        <v>219.10363636363638</v>
+      </c>
+      <c r="G30">
+        <f>AVERAGE(G3:G16)</f>
+        <v>214.80909090909097</v>
+      </c>
+      <c r="H30">
+        <f>AVERAGE(H3:H16)</f>
+        <v>219.30181818181819</v>
+      </c>
+      <c r="I30">
+        <f>AVERAGE(I3:I16)</f>
+        <v>221.55454545454549</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="0"/>
+        <v>218.00142857142859</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="0"/>
+        <v>227.31428571428569</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31">
+        <f>STDEV(B3:B18)</f>
+        <v>8.535498594106846</v>
+      </c>
+      <c r="C31">
+        <f>STDEV(C3:C18)</f>
+        <v>31.880128999111687</v>
+      </c>
+      <c r="D31">
+        <f t="shared" ref="D31:K31" si="1">STDEV(D3:D10)</f>
+        <v>5.566716780498691</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="1"/>
+        <v>26.096329106928799</v>
+      </c>
+      <c r="F31">
+        <f>STDEV(F3:F16)</f>
+        <v>6.1411615720924839</v>
+      </c>
+      <c r="G31">
+        <f>STDEV(G3:G16)</f>
+        <v>33.703218082119108</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>7.936833751566172</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="1"/>
+        <v>33.237554061633368</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="1"/>
+        <v>9.3359555840131758</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>9.6131853895227284</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B30:K30">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF7128"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:W19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="13.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" customWidth="1"/>
+    <col min="3" max="5" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="6.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:23">
+      <c r="A3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="V3">
+        <v>150</v>
+      </c>
+      <c r="W3">
+        <f>_xlfn.NORM.DIST(V3,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>1.3191266484266163E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="V4">
+        <v>160</v>
+      </c>
+      <c r="W4">
+        <f>_xlfn.NORM.DIST(V4,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>2.4859306893578424E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" s="17">
+        <v>150</v>
+      </c>
+      <c r="B5" s="18">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>170</v>
+      </c>
+      <c r="W5">
+        <f>_xlfn.NORM.DIST(V5,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>4.225175141815243E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" s="17">
+        <v>160</v>
+      </c>
+      <c r="B6" s="18">
+        <v>2</v>
+      </c>
+      <c r="V6">
+        <v>180</v>
+      </c>
+      <c r="W6">
+        <f>_xlfn.NORM.DIST(V6,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>6.4766972164444301E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" s="17">
+        <v>170</v>
+      </c>
+      <c r="B7" s="18">
+        <v>9</v>
+      </c>
+      <c r="V7">
+        <v>190</v>
+      </c>
+      <c r="W7">
+        <f>_xlfn.NORM.DIST(V7,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>8.9539703302276355E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" s="17">
+        <v>180</v>
+      </c>
+      <c r="B8" s="18">
+        <v>5</v>
+      </c>
+      <c r="V8">
+        <v>200</v>
+      </c>
+      <c r="W8">
+        <f>_xlfn.NORM.DIST(V8,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>1.1164284259627054E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" s="17">
+        <v>190</v>
+      </c>
+      <c r="B9" s="18">
+        <v>15</v>
+      </c>
+      <c r="V9">
+        <v>210</v>
+      </c>
+      <c r="W9">
+        <f>_xlfn.NORM.DIST(V9,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>1.2554496464711684E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" s="17">
+        <v>200</v>
+      </c>
+      <c r="B10" s="18">
+        <v>2</v>
+      </c>
+      <c r="V10">
+        <v>220</v>
+      </c>
+      <c r="W10">
+        <f>_xlfn.NORM.DIST(V10,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>1.2732711237242653E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" s="17">
+        <v>210</v>
+      </c>
+      <c r="B11" s="18">
+        <v>18</v>
+      </c>
+      <c r="V11">
+        <v>230</v>
+      </c>
+      <c r="W11">
+        <f>_xlfn.NORM.DIST(V11,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>1.1646506121258945E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" s="17">
+        <v>220</v>
+      </c>
+      <c r="B12" s="18">
+        <v>9</v>
+      </c>
+      <c r="V12">
+        <v>240</v>
+      </c>
+      <c r="W12">
+        <f>_xlfn.NORM.DIST(V12,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>9.607792319486835E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" s="17">
+        <v>230</v>
+      </c>
+      <c r="B13" s="18">
+        <v>9</v>
+      </c>
+      <c r="V13">
+        <v>250</v>
+      </c>
+      <c r="W13">
+        <f>_xlfn.NORM.DIST(V13,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>7.1483322926474855E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" s="17">
+        <v>240</v>
+      </c>
+      <c r="B14" s="18">
+        <v>7</v>
+      </c>
+      <c r="V14">
+        <v>260</v>
+      </c>
+      <c r="W14">
+        <f>_xlfn.NORM.DIST(V14,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>4.7966611154132387E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" s="17">
+        <v>250</v>
+      </c>
+      <c r="B15" s="18">
+        <v>13</v>
+      </c>
+      <c r="V15">
+        <v>270</v>
+      </c>
+      <c r="W15">
+        <f>_xlfn.NORM.DIST(V15,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>2.9028628589170603E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" s="17">
+        <v>260</v>
+      </c>
+      <c r="B16" s="18">
+        <v>3</v>
+      </c>
+      <c r="V16">
+        <v>280</v>
+      </c>
+      <c r="W16">
+        <f>_xlfn.NORM.DIST(V16,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>1.5844085565882061E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="17">
+        <v>270</v>
+      </c>
+      <c r="B17" s="18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="17">
+        <v>280</v>
+      </c>
+      <c r="B18" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="18">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
+      <mx:PLV Mode="0" OnePage="0" WScale="0"/>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J200"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18">
+      <c r="A2" s="21">
         <v>42019</v>
       </c>
-      <c r="B7">
-        <v>222.26</v>
-      </c>
-      <c r="C7">
-        <v>220.3</v>
-      </c>
-      <c r="D7">
+      <c r="B2" s="19">
         <v>235.4</v>
       </c>
-      <c r="E7">
+      <c r="C2" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="20">
+        <v>0</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <f>ROUND(B2/10,0)*10</f>
+        <v>240</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>AVERAGE(B:B)</f>
+        <v>216.36500000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="18">
+      <c r="A3" s="21">
+        <v>42020</v>
+      </c>
+      <c r="B3" s="19">
+        <v>170.9</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="20">
+        <v>0</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="0">ROUND(B3/10,0)*10</f>
+        <v>170</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>_xlfn.STDEV.S(B:B)</f>
+        <v>31.119049266851356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="18">
+      <c r="A4" s="21">
+        <v>42020</v>
+      </c>
+      <c r="B4" s="19">
+        <v>219.7</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="20">
+        <v>0</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="18">
+      <c r="A5" s="21">
+        <v>42021</v>
+      </c>
+      <c r="B5" s="19">
+        <v>240.4</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="20">
+        <v>0</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="18">
+      <c r="A6" s="21">
+        <v>42022</v>
+      </c>
+      <c r="B6" s="19">
+        <v>206.4</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="20">
+        <v>0</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="18">
+      <c r="A7" s="21">
+        <v>42023</v>
+      </c>
+      <c r="B7" s="19">
+        <v>256.2</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="18">
+      <c r="A8" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B8" s="19">
+        <v>225.5</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="20">
+        <v>0</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
         <v>230</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="1">
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="18">
+      <c r="A9" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B9" s="19">
+        <v>247.5</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="20">
+        <v>0</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="18">
+      <c r="A10" s="21">
+        <v>42026</v>
+      </c>
+      <c r="B10" s="19">
+        <v>189.9</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="18">
+      <c r="A11" s="21">
+        <v>42027</v>
+      </c>
+      <c r="B11" s="19">
+        <v>281.3</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="20">
+        <v>0</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="18">
+      <c r="A12" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B12" s="19">
+        <v>213.4</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="20">
+        <v>0</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="18">
+      <c r="A13" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B13" s="19">
+        <v>214.8</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="20">
+        <v>0</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="18">
+      <c r="A14" s="21">
+        <v>41667</v>
+      </c>
+      <c r="B14" s="19">
+        <v>207.2</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="20">
+        <v>0</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="18">
+      <c r="A15" s="21">
+        <v>41666</v>
+      </c>
+      <c r="B15" s="19">
+        <v>162.4</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="20">
+        <v>0</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="18">
+      <c r="A16" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B16" s="19">
+        <v>249.2</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="20">
+        <v>0</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="18">
+      <c r="A17" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B17" s="19">
+        <v>191.1</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="20">
+        <v>0</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="18">
+      <c r="A18" s="21">
+        <v>42019</v>
+      </c>
+      <c r="B18" s="19">
+        <v>230</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="20">
+        <v>8</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="18">
+      <c r="A19" s="21">
         <v>42020</v>
       </c>
+      <c r="B19" s="19">
+        <v>172.8</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="20">
+        <v>8</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="18">
+      <c r="A20" s="21">
+        <v>42020</v>
+      </c>
+      <c r="B20" s="19">
+        <v>219.7</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="20">
+        <v>8</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="18">
+      <c r="A21" s="21">
+        <v>42021</v>
+      </c>
+      <c r="B21" s="19">
+        <v>192.3</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="20">
+        <v>8</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="18">
+      <c r="A22" s="21">
+        <v>42022</v>
+      </c>
+      <c r="B22" s="19">
+        <v>206.4</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="20">
+        <v>8</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="18">
+      <c r="A23" s="21">
+        <v>42023</v>
+      </c>
+      <c r="B23" s="19">
+        <v>258.7</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="20">
+        <v>8</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="18">
+      <c r="A24" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B24" s="19">
+        <v>226.9</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="20">
+        <v>8</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="18">
+      <c r="A25" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B25" s="19">
+        <v>225.9</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="20">
+        <v>8</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="18">
+      <c r="A26" s="21">
+        <v>42026</v>
+      </c>
+      <c r="B26" s="19">
+        <v>177</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="20">
+        <v>8</v>
+      </c>
+      <c r="E26" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="18">
+      <c r="A27" s="21">
+        <v>42027</v>
+      </c>
+      <c r="B27" s="19">
+        <v>231.8</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="20">
+        <v>8</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="18">
+      <c r="A28" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B28" s="19">
+        <v>194.9</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="20">
+        <v>8</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="18">
+      <c r="A29" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B29" s="19">
+        <v>214.8</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="20">
+        <v>8</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="18">
+      <c r="A30" s="21">
+        <v>41667</v>
+      </c>
+      <c r="B30" s="19">
+        <v>208.3</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="20">
+        <v>8</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="18">
+      <c r="A31" s="21">
+        <v>41666</v>
+      </c>
+      <c r="B31" s="19">
+        <v>166.8</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="20">
+        <v>8</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="18">
+      <c r="A32" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B32" s="19">
+        <v>270</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="20">
+        <v>8</v>
+      </c>
+      <c r="E32" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>270</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="18">
+      <c r="A33" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B33" s="19">
+        <v>191.1</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="20">
+        <v>8</v>
+      </c>
+      <c r="E33" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="18">
+      <c r="A34" s="21">
+        <v>42021</v>
+      </c>
+      <c r="B34" s="19">
+        <v>192.3</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="20">
+        <v>0</v>
+      </c>
+      <c r="E34" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="18">
+      <c r="A35" s="21">
+        <v>42022</v>
+      </c>
+      <c r="B35" s="19">
+        <v>206.4</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="20">
+        <v>0</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="18">
+      <c r="A36" s="21">
+        <v>42023</v>
+      </c>
+      <c r="B36" s="19">
+        <v>253.8</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="20">
+        <v>0</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="18">
+      <c r="A37" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B37" s="19">
+        <v>226.9</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="18">
+      <c r="A38" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B38" s="19">
+        <v>248.4</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="20">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="18">
+      <c r="A39" s="21">
+        <v>42026</v>
+      </c>
+      <c r="B39" s="19">
+        <v>189.9</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="20">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="18">
+      <c r="A40" s="21">
+        <v>42027</v>
+      </c>
+      <c r="B40" s="19">
+        <v>271.5</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="20">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>270</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="18">
+      <c r="A41" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B41" s="19">
+        <v>205.9</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="20">
+        <v>0</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="18">
+      <c r="A42" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B42" s="19">
+        <v>213.5</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="20">
+        <v>0</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="18">
+      <c r="A43" s="21">
+        <v>41667</v>
+      </c>
+      <c r="B43" s="19">
+        <v>202</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="20">
+        <v>0</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="18">
+      <c r="A44" s="21">
+        <v>41666</v>
+      </c>
+      <c r="B44" s="19">
+        <v>152.30000000000001</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="20">
+        <v>0</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="18">
+      <c r="A45" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B45" s="19">
+        <v>249.2</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="20">
+        <v>0</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="18">
+      <c r="A46" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B46" s="19">
+        <v>191.1</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="20">
+        <v>0</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="18">
+      <c r="A47" s="21">
+        <v>42021</v>
+      </c>
+      <c r="B47" s="19">
+        <v>192.3</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="20">
+        <v>8</v>
+      </c>
+      <c r="E47" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="18">
+      <c r="A48" s="21">
+        <v>42022</v>
+      </c>
+      <c r="B48" s="19">
+        <v>206.4</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="20">
+        <v>8</v>
+      </c>
+      <c r="E48" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="18">
+      <c r="A49" s="21">
+        <v>42023</v>
+      </c>
+      <c r="B49" s="19">
+        <v>275.2</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="20">
+        <v>8</v>
+      </c>
+      <c r="E49" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="18">
+      <c r="A50" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B50" s="19">
+        <v>226.9</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="20">
+        <v>8</v>
+      </c>
+      <c r="E50" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="18">
+      <c r="A51" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B51" s="19">
+        <v>249.7</v>
+      </c>
+      <c r="C51" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="20">
+        <v>8</v>
+      </c>
+      <c r="E51" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="18">
+      <c r="A52" s="21">
+        <v>42026</v>
+      </c>
+      <c r="B52" s="19">
+        <v>213.8</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="20">
+        <v>8</v>
+      </c>
+      <c r="E52" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="18">
+      <c r="A53" s="21">
+        <v>42027</v>
+      </c>
+      <c r="B53" s="19">
+        <v>252</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" s="20">
+        <v>8</v>
+      </c>
+      <c r="E53" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="18">
+      <c r="A54" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B54" s="19">
+        <v>227.9</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="20">
+        <v>8</v>
+      </c>
+      <c r="E54" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="18">
+      <c r="A55" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B55" s="19">
+        <v>215.8</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="20">
+        <v>8</v>
+      </c>
+      <c r="E55" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="18">
+      <c r="A56" s="21">
+        <v>41667</v>
+      </c>
+      <c r="B56" s="19">
+        <v>213.8</v>
+      </c>
+      <c r="C56" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="20">
+        <v>8</v>
+      </c>
+      <c r="E56" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="18">
+      <c r="A57" s="21">
+        <v>41666</v>
+      </c>
+      <c r="B57" s="19">
+        <v>163.30000000000001</v>
+      </c>
+      <c r="C57" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="20">
+        <v>8</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="18">
+      <c r="A58" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B58" s="19">
+        <v>220.7</v>
+      </c>
+      <c r="C58" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="20">
+        <v>8</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="18">
+      <c r="A59" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B59" s="19">
+        <v>191.1</v>
+      </c>
+      <c r="C59" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="20">
+        <v>8</v>
+      </c>
+      <c r="E59" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="0"/>
+        <v>190</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="18">
+      <c r="A60" s="21">
+        <v>42022</v>
+      </c>
+      <c r="B60" s="19">
+        <v>243.3</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="20">
+        <v>8</v>
+      </c>
+      <c r="E60" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="18">
+      <c r="A61" s="21">
+        <v>42023</v>
+      </c>
+      <c r="B61" s="19">
+        <v>249.7</v>
+      </c>
+      <c r="C61" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="20">
+        <v>8</v>
+      </c>
+      <c r="E61" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="0"/>
+        <v>250</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="18">
+      <c r="A62" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B62" s="19">
+        <v>226.9</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="20">
+        <v>8</v>
+      </c>
+      <c r="E62" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="18">
+      <c r="A63" s="21">
+        <v>42024</v>
+      </c>
+      <c r="B63" s="19">
+        <v>240.9</v>
+      </c>
+      <c r="C63" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="20">
+        <v>8</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="18">
+      <c r="A64" s="21">
+        <v>42026</v>
+      </c>
+      <c r="B64" s="19">
+        <v>213.8</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="20">
+        <v>8</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="0"/>
+        <v>210</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="18">
+      <c r="A65" s="21">
+        <v>42027</v>
+      </c>
+      <c r="B65" s="19">
+        <v>243.6</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="20">
+        <v>8</v>
+      </c>
+      <c r="E65" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="0"/>
+        <v>240</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="18">
+      <c r="A66" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B66" s="19">
+        <v>173</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="20">
+        <v>8</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="0"/>
+        <v>170</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="18">
+      <c r="A67" s="21">
+        <v>41664</v>
+      </c>
+      <c r="B67" s="19">
+        <v>186.6</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" s="20">
+        <v>8</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67">
+        <f t="shared" ref="F67:F96" si="1">ROUND(B67/10,0)*10</f>
+        <v>190</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="18">
+      <c r="A68" s="21">
+        <v>41667</v>
+      </c>
+      <c r="B68" s="19">
+        <v>199.6</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="20">
+        <v>8</v>
+      </c>
+      <c r="E68" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="18">
+      <c r="A69" s="21">
+        <v>41666</v>
+      </c>
+      <c r="B69" s="19">
+        <v>177.9</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="20">
+        <v>8</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="18">
+      <c r="A70" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B70" s="19">
+        <v>220.7</v>
+      </c>
+      <c r="C70" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="20">
+        <v>8</v>
+      </c>
+      <c r="E70" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="18">
+      <c r="A71" s="21">
+        <v>41665</v>
+      </c>
+      <c r="B71" s="19">
+        <v>188.2</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="20">
+        <v>8</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="18">
+      <c r="A72" s="1">
+        <v>42033</v>
+      </c>
+      <c r="B72" s="19">
+        <v>271.10000000000002</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="20">
+        <v>8</v>
+      </c>
+      <c r="E72" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="18">
+      <c r="A73" s="1">
+        <v>42033</v>
+      </c>
+      <c r="B73" s="19">
+        <v>271.10000000000002</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="20">
+        <v>8</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="18">
+      <c r="A74" s="1">
+        <v>42033</v>
+      </c>
+      <c r="B74" s="19">
+        <v>271.10000000000002</v>
+      </c>
+      <c r="C74" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="20">
+        <v>0</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="18">
+      <c r="A75" s="1">
+        <v>42033</v>
+      </c>
+      <c r="B75" s="19">
+        <v>218.7</v>
+      </c>
+      <c r="C75" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="20">
+        <v>0</v>
+      </c>
+      <c r="E75" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="18">
+      <c r="A76" s="1">
+        <v>42033</v>
+      </c>
+      <c r="B76" s="19">
+        <v>264.8</v>
+      </c>
+      <c r="C76" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D76" s="20">
+        <v>8</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="18">
+      <c r="A77" s="1">
+        <v>42034</v>
+      </c>
+      <c r="B77" s="19">
+        <v>173.7</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="20">
+        <v>8</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="18">
+      <c r="A78" s="1">
+        <v>42034</v>
+      </c>
+      <c r="B78" s="19">
+        <v>173.7</v>
+      </c>
+      <c r="C78" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="20">
+        <v>8</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="18">
+      <c r="A79" s="1">
+        <v>42034</v>
+      </c>
+      <c r="B79" s="19">
+        <v>173.7</v>
+      </c>
+      <c r="C79" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" s="20">
+        <v>0</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="18">
+      <c r="A80" s="1">
+        <v>42034</v>
+      </c>
+      <c r="B80" s="19">
+        <v>173.7</v>
+      </c>
+      <c r="C80" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="20">
+        <v>0</v>
+      </c>
+      <c r="E80" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="18">
+      <c r="A81" s="1">
+        <v>42034</v>
+      </c>
+      <c r="B81" s="19">
+        <v>173.7</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81" s="20">
+        <v>8</v>
+      </c>
+      <c r="E81" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81">
+        <f t="shared" si="1"/>
+        <v>170</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="25">
+      <c r="A82" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B82" s="19">
+        <v>191.5</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" s="20">
+        <v>8</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="G82" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="25">
+      <c r="A83" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B83" s="19">
+        <v>178.6</v>
+      </c>
+      <c r="C83" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="20">
+        <v>8</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="G83" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="25">
+      <c r="A84" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B84" s="19">
+        <v>178.7</v>
+      </c>
+      <c r="C84" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" s="20">
+        <v>0</v>
+      </c>
+      <c r="E84" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="G84" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="25">
+      <c r="A85" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B85" s="19">
+        <v>191.5</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="20">
+        <v>0</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="G85" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="25">
+      <c r="A86" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B86" s="19">
+        <v>217.7</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D86" s="20">
+        <v>8</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="G86" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="25">
+      <c r="A87" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B87" s="19">
+        <v>219.3</v>
+      </c>
+      <c r="C87" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" s="20">
+        <v>8</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+      <c r="G87" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="25">
+      <c r="A88" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B88" s="19">
+        <v>205.4</v>
+      </c>
+      <c r="C88" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D88" s="20">
+        <v>8</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="G88" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="25">
+      <c r="A89" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B89" s="19">
+        <v>185.9</v>
+      </c>
+      <c r="C89" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D89" s="20">
+        <v>0</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="G89" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="25">
+      <c r="A90" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B90" s="19">
+        <v>179.4</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D90" s="20">
+        <v>0</v>
+      </c>
+      <c r="E90" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90">
+        <f t="shared" si="1"/>
+        <v>180</v>
+      </c>
+      <c r="G90" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="25">
+      <c r="A91" s="1">
+        <v>42035</v>
+      </c>
+      <c r="B91" s="19">
+        <v>212.8</v>
+      </c>
+      <c r="C91" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D91" s="20">
+        <v>8</v>
+      </c>
+      <c r="E91" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
+      <c r="G91" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="25">
+      <c r="A92" s="1">
+        <v>42036</v>
+      </c>
+      <c r="B92" s="19">
+        <v>254.5</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="20">
+        <v>0</v>
+      </c>
+      <c r="E92" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="G92" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="25">
+      <c r="A93" s="1">
+        <v>42036</v>
+      </c>
+      <c r="B93" s="19">
+        <v>254.5</v>
+      </c>
+      <c r="C93" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="20">
+        <v>8</v>
+      </c>
+      <c r="E93" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F93">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="G93" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="25">
+      <c r="A94" s="1">
+        <v>42036</v>
+      </c>
+      <c r="B94" s="19">
+        <v>254.5</v>
+      </c>
+      <c r="C94" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" s="20">
+        <v>0</v>
+      </c>
+      <c r="E94" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="G94" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="25">
+      <c r="A95" s="1">
+        <v>42036</v>
+      </c>
+      <c r="B95" s="19">
+        <v>254.5</v>
+      </c>
+      <c r="C95" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" s="20">
+        <v>8</v>
+      </c>
+      <c r="E95" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="G95" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="25">
+      <c r="A96" s="1">
+        <v>42036</v>
+      </c>
+      <c r="B96" s="19">
+        <v>254.5</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="20">
+        <v>8</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="G96" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="25">
+      <c r="A97" s="1">
+        <v>42037</v>
+      </c>
+      <c r="B97" s="19">
+        <v>211.6</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D97" s="20">
+        <v>0</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97">
+        <f t="shared" ref="F97:F101" si="2">ROUND(B97/10,0)*10</f>
+        <v>210</v>
+      </c>
+      <c r="G97" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="25">
+      <c r="A98" s="1">
+        <v>42037</v>
+      </c>
+      <c r="B98" s="19">
+        <v>215.6</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" s="20">
+        <v>8</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98">
+        <f t="shared" si="2"/>
+        <v>220</v>
+      </c>
+      <c r="G98" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="25">
+      <c r="A99" s="1">
+        <v>42037</v>
+      </c>
+      <c r="B99" s="19">
+        <v>214.7</v>
+      </c>
+      <c r="C99" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D99" s="20">
+        <v>0</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99">
+        <f t="shared" si="2"/>
+        <v>210</v>
+      </c>
+      <c r="G99" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="25">
+      <c r="A100" s="1">
+        <v>42037</v>
+      </c>
+      <c r="B100" s="19">
+        <v>242</v>
+      </c>
+      <c r="C100" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="20">
+        <v>8</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="G100" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="25">
+      <c r="A101" s="1">
+        <v>42037</v>
+      </c>
+      <c r="B101" s="19">
+        <v>239</v>
+      </c>
+      <c r="C101" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101" s="20">
+        <v>8</v>
+      </c>
+      <c r="E101" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101">
+        <f t="shared" si="2"/>
+        <v>240</v>
+      </c>
+      <c r="G101" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="25">
+      <c r="A102" s="1">
+        <v>42038</v>
+      </c>
+      <c r="B102" s="19"/>
+      <c r="C102" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="20">
+        <v>0</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="25">
+      <c r="A103" s="1">
+        <v>42038</v>
+      </c>
+      <c r="B103" s="19"/>
+      <c r="C103" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="20">
+        <v>8</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="25">
+      <c r="A104" s="1">
+        <v>42038</v>
+      </c>
+      <c r="B104" s="19"/>
+      <c r="C104" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" s="20">
+        <v>0</v>
+      </c>
+      <c r="E104" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G104" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="25">
+      <c r="A105" s="1">
+        <v>42038</v>
+      </c>
+      <c r="B105" s="19"/>
+      <c r="C105" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="20">
+        <v>8</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G105" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="25">
+      <c r="A106" s="1">
+        <v>42038</v>
+      </c>
+      <c r="B106" s="19"/>
+      <c r="C106" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D106" s="20">
+        <v>8</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G106" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="I107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="I108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="I109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="I110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="I111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="I112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="9:9">
+      <c r="I113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="9:9">
+      <c r="I114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="9:9">
+      <c r="I115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="9:9">
+      <c r="I116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="9:9">
+      <c r="I117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="9:9">
+      <c r="I118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="9:9">
+      <c r="I119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="9:9">
+      <c r="I120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="9:9">
+      <c r="I121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="9:9">
+      <c r="I122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="9:9">
+      <c r="I123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="9:9">
+      <c r="I124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="9:9">
+      <c r="I125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="9:9">
+      <c r="I126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="9:9">
+      <c r="I127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="9:9">
+      <c r="I128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="9:9">
+      <c r="I129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="9:9">
+      <c r="I130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="9:9">
+      <c r="I131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="9:9">
+      <c r="I132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="9:9">
+      <c r="I133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="9:9">
+      <c r="I134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="9:9">
+      <c r="I135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="9:9">
+      <c r="I136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="9:9">
+      <c r="I137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="9:9">
+      <c r="I138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="9:9">
+      <c r="I139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="9:9">
+      <c r="I140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="9:9">
+      <c r="I141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="9:9">
+      <c r="I142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="9:9">
+      <c r="I143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="9:9">
+      <c r="I144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="9:9">
+      <c r="I145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="9:9">
+      <c r="I146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="9:9">
+      <c r="I147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="9:9">
+      <c r="I148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="9:9">
+      <c r="I149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="9:9">
+      <c r="I150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="9:9">
+      <c r="I151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="9:9">
+      <c r="I152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="9:9">
+      <c r="I153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="9:9">
+      <c r="I154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="9:9">
+      <c r="I155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="9:9">
+      <c r="I156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="9:9">
+      <c r="I157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="9:9">
+      <c r="I158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="9:9">
+      <c r="I159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="9:9">
+      <c r="I160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="9:9">
+      <c r="I161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="9:9">
+      <c r="I162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="9:9">
+      <c r="I163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="9:9">
+      <c r="I164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="9:9">
+      <c r="I165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="9:9">
+      <c r="I166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="9:9">
+      <c r="I167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="9:9">
+      <c r="I168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="9:9">
+      <c r="I169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="9:9">
+      <c r="I170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="9:9">
+      <c r="I171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="9:9">
+      <c r="I172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="9:9">
+      <c r="I173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="9:9">
+      <c r="I174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="9:9">
+      <c r="I175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="9:9">
+      <c r="I176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="9:9">
+      <c r="I177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="9:9">
+      <c r="I178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="9:9">
+      <c r="I179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="9:9">
+      <c r="I180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="9:9">
+      <c r="I181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="9:9">
+      <c r="I182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="9:9">
+      <c r="I183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="9:9">
+      <c r="I184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="9:9">
+      <c r="I185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="9:9">
+      <c r="I186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="9:9">
+      <c r="I187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="9:9">
+      <c r="I188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="9:9">
+      <c r="I189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="9:9">
+      <c r="I190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="9:9">
+      <c r="I191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="9:9">
+      <c r="I192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="9:9">
+      <c r="I193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="9:9">
+      <c r="I194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="9:9">
+      <c r="I195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="9:9">
+      <c r="I196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="9:9">
+      <c r="I197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="9:9">
+      <c r="I198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="9:9">
+      <c r="I199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="9:9">
+      <c r="I200">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -4,16 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
   <workbookPr showInkAnnotation="0" hidePivotFieldList="1" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="15540" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="1120" yWindow="1120" windowWidth="24480" windowHeight="14420" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet5" sheetId="5" r:id="rId2"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="140000" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="140000" concurrentCalc="0"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId4"/>
+    <pivotCache cacheId="3" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="73">
   <si>
     <t>Date</t>
   </si>
@@ -145,6 +145,105 @@
   <si>
     <t>S130000006</t>
   </si>
+  <si>
+    <t>S130611118</t>
+  </si>
+  <si>
+    <t>S130611542</t>
+  </si>
+  <si>
+    <t>S130611988</t>
+  </si>
+  <si>
+    <t>S130612327</t>
+  </si>
+  <si>
+    <t>S130612801</t>
+  </si>
+  <si>
+    <t>S131244958</t>
+  </si>
+  <si>
+    <t>S131245950</t>
+  </si>
+  <si>
+    <t>S132293712</t>
+  </si>
+  <si>
+    <t>S132294089</t>
+  </si>
+  <si>
+    <t>S132533642</t>
+  </si>
+  <si>
+    <t>S132535745</t>
+  </si>
+  <si>
+    <t>S132537184</t>
+  </si>
+  <si>
+    <t>S133093188</t>
+  </si>
+  <si>
+    <t>S133094607</t>
+  </si>
+  <si>
+    <t>S133095435</t>
+  </si>
+  <si>
+    <t>S133097181</t>
+  </si>
+  <si>
+    <t>NN</t>
+  </si>
+  <si>
+    <t>S133641750</t>
+  </si>
+  <si>
+    <t>S133642428</t>
+  </si>
+  <si>
+    <t>S133642781</t>
+  </si>
+  <si>
+    <t>S133643274</t>
+  </si>
+  <si>
+    <t>S134270174</t>
+  </si>
+  <si>
+    <t>S134269016</t>
+  </si>
+  <si>
+    <t>S134269582</t>
+  </si>
+  <si>
+    <t>S134271406</t>
+  </si>
+  <si>
+    <t>S134271964</t>
+  </si>
+  <si>
+    <t>S135020132</t>
+  </si>
+  <si>
+    <t>S135020740</t>
+  </si>
+  <si>
+    <t>S135023095</t>
+  </si>
+  <si>
+    <t>S135023734</t>
+  </si>
+  <si>
+    <t>S135326936</t>
+  </si>
+  <si>
+    <t>S135327115</t>
+  </si>
+  <si>
+    <t>S135327370</t>
+  </si>
 </sst>
 </file>
 
@@ -156,6 +255,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -254,7 +354,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="115">
+  <cellStyleXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -337,6 +437,53 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -401,7 +548,7 @@
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="115">
+  <cellStyles count="162">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -459,6 +606,30 @@
     <cellStyle name="Followed Hyperlink" xfId="110" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="112" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="114" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="116" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="118" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="120" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="122" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="124" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="126" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="128" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="129" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="131" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="133" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="135" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="137" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="139" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="141" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="143" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="145" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="147" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="149" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="151" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="153" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="155" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="157" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="159" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="161" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -516,6 +687,29 @@
     <cellStyle name="Hyperlink" xfId="109" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="111" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="113" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="115" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="117" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="119" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="121" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="123" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="125" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="127" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="130" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="132" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="134" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="136" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="138" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="140" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="142" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="144" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="146" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="148" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="150" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="152" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="154" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="156" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="158" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="160" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -550,10 +744,10 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet5!$A$5:$A$18</c:f>
+              <c:f>Sheet5!$A$5:$A$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>150.0</c:v>
                 </c:pt>
@@ -596,56 +790,62 @@
                 <c:pt idx="13">
                   <c:v>280.0</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>290.0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet5!$B$5:$B$18</c:f>
+              <c:f>Sheet5!$B$5:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0</c:v>
+                  <c:v>5.0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.0</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.0</c:v>
+                  <c:v>19.0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.0</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18.0</c:v>
+                  <c:v>28.0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.0</c:v>
+                  <c:v>20.0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.0</c:v>
+                  <c:v>13.0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.0</c:v>
+                  <c:v>11.0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.0</c:v>
+                  <c:v>14.0</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>3.0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>5.0</c:v>
+                  <c:v>9.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2.0</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -660,8 +860,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="-2090754408"/>
-        <c:axId val="-2133061752"/>
+        <c:axId val="-2125646632"/>
+        <c:axId val="-2125738872"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -674,10 +874,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet5!$V$3:$V$16</c:f>
+              <c:f>Sheet5!$V$3:$V$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>150.0</c:v>
                 </c:pt>
@@ -720,56 +920,62 @@
                 <c:pt idx="13">
                   <c:v>280.0</c:v>
                 </c:pt>
+                <c:pt idx="14">
+                  <c:v>290.0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet5!$W$3:$W$16</c:f>
+              <c:f>Sheet5!$W$3:$W$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.00131912664842662</c:v>
+                  <c:v>0.00113936331686994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00248593068935784</c:v>
+                  <c:v>0.00223901419611758</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.00422517514181524</c:v>
+                  <c:v>0.00394603925093226</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00647669721644443</c:v>
+                  <c:v>0.00623700214952315</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00895397033022763</c:v>
+                  <c:v>0.00884097832545786</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0111642842596271</c:v>
+                  <c:v>0.0112391818255554</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0125544964647117</c:v>
+                  <c:v>0.012813831471045</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0127327112372427</c:v>
+                  <c:v>0.0131018691457743</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0116465061212589</c:v>
+                  <c:v>0.012014271630392</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.00960779231948683</c:v>
+                  <c:v>0.00988033283984121</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.00714833229264748</c:v>
+                  <c:v>0.00728711532168424</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.00479666111541324</c:v>
+                  <c:v>0.00482002897793604</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.00290286285891706</c:v>
+                  <c:v>0.00285925964781033</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.00158440855658821</c:v>
+                  <c:v>0.00152113402352969</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.00072575711948566</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -786,11 +992,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="-2090080968"/>
-        <c:axId val="-2090397352"/>
+        <c:axId val="-2125732408"/>
+        <c:axId val="-2125741912"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-2090080968"/>
+        <c:axId val="-2125732408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -800,7 +1006,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2090397352"/>
+        <c:crossAx val="-2125741912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -808,7 +1014,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-2090397352"/>
+        <c:axId val="-2125741912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -819,12 +1025,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2090080968"/>
+        <c:crossAx val="-2125732408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-2133061752"/>
+        <c:axId val="-2125738872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -834,12 +1040,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2090754408"/>
+        <c:crossAx val="-2125646632"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="-2090754408"/>
+        <c:axId val="-2125646632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -849,7 +1055,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2133061752"/>
+        <c:crossAx val="-2125738872"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -910,16 +1116,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Jesse Green" refreshedDate="42038.406953587961" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="100">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Jesse Green" refreshedDate="42047.398584490744" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="147">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F101" sheet="Sheet4"/>
+    <worksheetSource ref="A1:F148" sheet="Sheet4"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2014-01-25T00:00:00" maxDate="2015-02-03T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2014-01-25T00:00:00" maxDate="2015-02-12T00:00:00"/>
     </cacheField>
     <cacheField name="score" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="152.30000000000001" maxValue="281.3"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="152.30000000000001" maxValue="291.10000000000002"/>
     </cacheField>
     <cacheField name="model" numFmtId="0">
       <sharedItems/>
@@ -931,7 +1137,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="rounded" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="150" maxValue="280" count="14">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="150" maxValue="290" count="15">
         <n v="240"/>
         <n v="170"/>
         <n v="220"/>
@@ -946,6 +1152,7 @@
         <n v="270"/>
         <n v="200"/>
         <n v="150"/>
+        <n v="290"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -958,7 +1165,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="100">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="147">
   <r>
     <d v="2015-01-15T00:00:00"/>
     <n v="235.4"/>
@@ -1758,13 +1965,389 @@
     <n v="8"/>
     <s v="l1"/>
     <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-03T00:00:00"/>
+    <n v="272.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-02-03T00:00:00"/>
+    <n v="272.2"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-02-03T00:00:00"/>
+    <n v="272.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-02-03T00:00:00"/>
+    <n v="272.2"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-02-03T00:00:00"/>
+    <n v="291.10000000000002"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="14"/>
+  </r>
+  <r>
+    <d v="2015-02-04T00:00:00"/>
+    <n v="213"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-04T00:00:00"/>
+    <n v="229.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-04T00:00:00"/>
+    <n v="199.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-04T00:00:00"/>
+    <n v="210.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-04T00:00:00"/>
+    <n v="218"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-05T00:00:00"/>
+    <n v="223.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-05T00:00:00"/>
+    <n v="223.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-05T00:00:00"/>
+    <n v="223.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-05T00:00:00"/>
+    <n v="223.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-05T00:00:00"/>
+    <n v="218.2"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="208.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="208.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="208.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="208.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="212.2"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="239.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="239.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="229.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="239.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-06T00:00:00"/>
+    <n v="213.7"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-07T00:00:00"/>
+    <n v="232.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-07T00:00:00"/>
+    <n v="188.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-07T00:00:00"/>
+    <n v="232.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-07T00:00:00"/>
+    <n v="188.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-07T00:00:00"/>
+    <n v="244"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-07T00:00:00"/>
+    <n v="248.9"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-08T00:00:00"/>
+    <n v="159.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <d v="2015-02-08T00:00:00"/>
+    <n v="159.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <d v="2015-02-08T00:00:00"/>
+    <n v="159.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <d v="2015-02-08T00:00:00"/>
+    <n v="187.1"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-08T00:00:00"/>
+    <n v="194.6"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-08T00:00:00"/>
+    <n v="176.7"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-02-09T00:00:00"/>
+    <n v="210.6"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-09T00:00:00"/>
+    <n v="203.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-09T00:00:00"/>
+    <n v="221.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-09T00:00:00"/>
+    <n v="221.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-09T00:00:00"/>
+    <n v="218.5"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-09T00:00:00"/>
+    <n v="199.8"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-11T00:00:00"/>
+    <n v="205.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-11T00:00:00"/>
+    <n v="222"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-11T00:00:00"/>
+    <n v="203.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-11T00:00:00"/>
+    <n v="219.4"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
-  <location ref="A3:B19" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
+  <location ref="A3:B20" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -1772,7 +2355,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="15">
+      <items count="16">
         <item x="13"/>
         <item x="9"/>
         <item x="1"/>
@@ -1787,6 +2370,7 @@
         <item x="4"/>
         <item x="11"/>
         <item x="8"/>
+        <item x="14"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1794,7 +2378,7 @@
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="15">
+  <rowItems count="16">
     <i>
       <x/>
     </i>
@@ -1836,6 +2420,9 @@
     </i>
     <i>
       <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
     </i>
     <i t="grand">
       <x/>
@@ -2889,7 +3476,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:W19"/>
+  <dimension ref="A3:W20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="13.1640625" customWidth="1"/>
@@ -2910,7 +3497,7 @@
       </c>
       <c r="W3">
         <f>_xlfn.NORM.DIST(V3,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.3191266484266163E-3</v>
+        <v>1.1393633168699394E-3</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -2925,7 +3512,7 @@
       </c>
       <c r="W4">
         <f>_xlfn.NORM.DIST(V4,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>2.4859306893578424E-3</v>
+        <v>2.2390141961175767E-3</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -2940,7 +3527,7 @@
       </c>
       <c r="W5">
         <f>_xlfn.NORM.DIST(V5,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>4.225175141815243E-3</v>
+        <v>3.9460392509322595E-3</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -2948,14 +3535,14 @@
         <v>160</v>
       </c>
       <c r="B6" s="18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>180</v>
       </c>
       <c r="W6">
         <f>_xlfn.NORM.DIST(V6,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>6.4766972164444301E-3</v>
+        <v>6.2370021495231475E-3</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -2970,7 +3557,7 @@
       </c>
       <c r="W7">
         <f>_xlfn.NORM.DIST(V7,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>8.9539703302276355E-3</v>
+        <v>8.8409783254578614E-3</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -2978,14 +3565,14 @@
         <v>180</v>
       </c>
       <c r="B8" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>200</v>
       </c>
       <c r="W8">
         <f>_xlfn.NORM.DIST(V8,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.1164284259627054E-2</v>
+        <v>1.1239181825555446E-2</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -2993,14 +3580,14 @@
         <v>190</v>
       </c>
       <c r="B9" s="18">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V9">
         <v>210</v>
       </c>
       <c r="W9">
         <f>_xlfn.NORM.DIST(V9,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.2554496464711684E-2</v>
+        <v>1.2813831471045038E-2</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -3008,14 +3595,14 @@
         <v>200</v>
       </c>
       <c r="B10" s="18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>220</v>
       </c>
       <c r="W10">
         <f>_xlfn.NORM.DIST(V10,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.2732711237242653E-2</v>
+        <v>1.3101869145774273E-2</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -3023,14 +3610,14 @@
         <v>210</v>
       </c>
       <c r="B11" s="18">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="V11">
         <v>230</v>
       </c>
       <c r="W11">
         <f>_xlfn.NORM.DIST(V11,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.1646506121258945E-2</v>
+        <v>1.2014271630391963E-2</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -3038,14 +3625,14 @@
         <v>220</v>
       </c>
       <c r="B12" s="18">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="V12">
         <v>240</v>
       </c>
       <c r="W12">
         <f>_xlfn.NORM.DIST(V12,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>9.607792319486835E-3</v>
+        <v>9.8803328398412143E-3</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -3053,14 +3640,14 @@
         <v>230</v>
       </c>
       <c r="B13" s="18">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V13">
         <v>250</v>
       </c>
       <c r="W13">
         <f>_xlfn.NORM.DIST(V13,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>7.1483322926474855E-3</v>
+        <v>7.2871153216842394E-3</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -3068,14 +3655,14 @@
         <v>240</v>
       </c>
       <c r="B14" s="18">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V14">
         <v>260</v>
       </c>
       <c r="W14">
         <f>_xlfn.NORM.DIST(V14,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>4.7966611154132387E-3</v>
+        <v>4.8200289779360391E-3</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -3083,14 +3670,14 @@
         <v>250</v>
       </c>
       <c r="B15" s="18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V15">
         <v>270</v>
       </c>
       <c r="W15">
         <f>_xlfn.NORM.DIST(V15,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>2.9028628589170603E-3</v>
+        <v>2.8592596478103334E-3</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -3105,18 +3692,25 @@
       </c>
       <c r="W16">
         <f>_xlfn.NORM.DIST(V16,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.5844085565882061E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>1.5211340235296864E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="17">
         <v>270</v>
       </c>
       <c r="B17" s="18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>9</v>
+      </c>
+      <c r="V17">
+        <v>290</v>
+      </c>
+      <c r="W17">
+        <f>_xlfn.NORM.DIST(V17,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>7.2575711948566013E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="17">
         <v>280</v>
       </c>
@@ -3124,12 +3718,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="17" t="s">
+    <row r="19" spans="1:23">
+      <c r="A19" s="17">
+        <v>290</v>
+      </c>
+      <c r="B19" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="18">
-        <v>100</v>
+      <c r="B20" s="18">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3200,7 +3802,7 @@
       </c>
       <c r="J2">
         <f>AVERAGE(B:B)</f>
-        <v>216.36500000000004</v>
+        <v>217.04149659863958</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="18">
@@ -3228,7 +3830,7 @@
       </c>
       <c r="J3">
         <f>_xlfn.STDEV.S(B:B)</f>
-        <v>31.119049266851356</v>
+        <v>30.304506748198964</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="18">
@@ -5647,7 +6249,9 @@
       <c r="A102" s="1">
         <v>42038</v>
       </c>
-      <c r="B102" s="19"/>
+      <c r="B102" s="19">
+        <v>272.2</v>
+      </c>
       <c r="C102" s="20" t="s">
         <v>12</v>
       </c>
@@ -5656,6 +6260,10 @@
       </c>
       <c r="E102" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F102">
+        <f>ROUND(B102/10,0)*10</f>
+        <v>270</v>
       </c>
       <c r="G102" s="22" t="s">
         <v>39</v>
@@ -5668,7 +6276,9 @@
       <c r="A103" s="1">
         <v>42038</v>
       </c>
-      <c r="B103" s="19"/>
+      <c r="B103" s="19">
+        <v>272.2</v>
+      </c>
       <c r="C103" s="20" t="s">
         <v>12</v>
       </c>
@@ -5677,6 +6287,10 @@
       </c>
       <c r="E103" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F103">
+        <f t="shared" ref="F103:F105" si="3">ROUND(B103/10,0)*10</f>
+        <v>270</v>
       </c>
       <c r="G103" s="22" t="s">
         <v>39</v>
@@ -5689,7 +6303,9 @@
       <c r="A104" s="1">
         <v>42038</v>
       </c>
-      <c r="B104" s="19"/>
+      <c r="B104" s="19">
+        <v>272.2</v>
+      </c>
       <c r="C104" s="20" t="s">
         <v>12</v>
       </c>
@@ -5698,6 +6314,10 @@
       </c>
       <c r="E104" s="19" t="s">
         <v>19</v>
+      </c>
+      <c r="F104">
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
       <c r="G104" s="22" t="s">
         <v>39</v>
@@ -5710,7 +6330,9 @@
       <c r="A105" s="1">
         <v>42038</v>
       </c>
-      <c r="B105" s="19"/>
+      <c r="B105" s="19">
+        <v>272.2</v>
+      </c>
       <c r="C105" s="20" t="s">
         <v>12</v>
       </c>
@@ -5719,6 +6341,10 @@
       </c>
       <c r="E105" s="19" t="s">
         <v>19</v>
+      </c>
+      <c r="F105">
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
       <c r="G105" s="22" t="s">
         <v>39</v>
@@ -5731,7 +6357,9 @@
       <c r="A106" s="1">
         <v>42038</v>
       </c>
-      <c r="B106" s="19"/>
+      <c r="B106" s="19">
+        <v>291.10000000000002</v>
+      </c>
       <c r="C106" s="20" t="s">
         <v>20</v>
       </c>
@@ -5741,6 +6369,10 @@
       <c r="E106" s="19" t="s">
         <v>19</v>
       </c>
+      <c r="F106">
+        <f t="shared" ref="F106:F148" si="4">ROUND(B106/10,0)*10</f>
+        <v>290</v>
+      </c>
       <c r="G106" s="22" t="s">
         <v>38</v>
       </c>
@@ -5748,272 +6380,1256 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" ht="25">
+      <c r="A107" s="1">
+        <v>42039</v>
+      </c>
+      <c r="B107" s="19">
+        <v>213</v>
+      </c>
+      <c r="C107" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="20">
+        <v>0</v>
+      </c>
+      <c r="E107" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G107" s="22" t="s">
+        <v>44</v>
+      </c>
       <c r="I107">
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" ht="25">
+      <c r="A108" s="1">
+        <v>42039</v>
+      </c>
+      <c r="B108" s="19">
+        <v>229.7</v>
+      </c>
+      <c r="C108" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" s="20">
+        <v>8</v>
+      </c>
+      <c r="E108" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108">
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="G108" s="22" t="s">
+        <v>43</v>
+      </c>
       <c r="I108">
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" ht="25">
+      <c r="A109" s="1">
+        <v>42039</v>
+      </c>
+      <c r="B109" s="19">
+        <v>199.2</v>
+      </c>
+      <c r="C109" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="20">
+        <v>0</v>
+      </c>
+      <c r="E109" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="G109" s="22" t="s">
+        <v>42</v>
+      </c>
       <c r="I109">
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" ht="25">
+      <c r="A110" s="1">
+        <v>42039</v>
+      </c>
+      <c r="B110" s="19">
+        <v>210.5</v>
+      </c>
+      <c r="C110" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="20">
+        <v>8</v>
+      </c>
+      <c r="E110" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G110" s="22" t="s">
+        <v>41</v>
+      </c>
       <c r="I110">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" ht="25">
+      <c r="A111" s="1">
+        <v>42039</v>
+      </c>
+      <c r="B111" s="19">
+        <v>218</v>
+      </c>
+      <c r="C111" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="20">
+        <v>8</v>
+      </c>
+      <c r="E111" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G111" s="22" t="s">
+        <v>40</v>
+      </c>
       <c r="I111">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" ht="25">
+      <c r="A112" s="1">
+        <v>42040</v>
+      </c>
+      <c r="B112" s="19">
+        <v>223.5</v>
+      </c>
+      <c r="C112" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" s="20">
+        <v>0</v>
+      </c>
+      <c r="E112" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G112" s="22" t="s">
+        <v>46</v>
+      </c>
       <c r="I112">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="9:9">
+    <row r="113" spans="1:9" ht="25">
+      <c r="A113" s="1">
+        <v>42040</v>
+      </c>
+      <c r="B113" s="19">
+        <v>223.5</v>
+      </c>
+      <c r="C113" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="20">
+        <v>8</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G113" s="22" t="s">
+        <v>46</v>
+      </c>
       <c r="I113">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="9:9">
+    <row r="114" spans="1:9" ht="25">
+      <c r="A114" s="1">
+        <v>42040</v>
+      </c>
+      <c r="B114" s="19">
+        <v>223.5</v>
+      </c>
+      <c r="C114" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" s="20">
+        <v>0</v>
+      </c>
+      <c r="E114" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G114" s="22" t="s">
+        <v>46</v>
+      </c>
       <c r="I114">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="9:9">
+    <row r="115" spans="1:9" ht="25">
+      <c r="A115" s="1">
+        <v>42040</v>
+      </c>
+      <c r="B115" s="19">
+        <v>223.5</v>
+      </c>
+      <c r="C115" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="20">
+        <v>8</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G115" s="22" t="s">
+        <v>46</v>
+      </c>
       <c r="I115">
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="9:9">
+    <row r="116" spans="1:9" ht="25">
+      <c r="A116" s="1">
+        <v>42040</v>
+      </c>
+      <c r="B116" s="19">
+        <v>218.2</v>
+      </c>
+      <c r="C116" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116" s="20">
+        <v>8</v>
+      </c>
+      <c r="E116" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F116">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G116" s="22" t="s">
+        <v>45</v>
+      </c>
       <c r="I116">
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="9:9">
+    <row r="117" spans="1:9" ht="25">
+      <c r="A117" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B117">
+        <v>208.5</v>
+      </c>
+      <c r="C117" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="20">
+        <v>0</v>
+      </c>
+      <c r="E117" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G117" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="I117">
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="9:9">
+    <row r="118" spans="1:9" ht="25">
+      <c r="A118" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B118">
+        <v>208.5</v>
+      </c>
+      <c r="C118" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="20">
+        <v>8</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G118" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="I118">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="9:9">
+    <row r="119" spans="1:9" ht="25">
+      <c r="A119" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B119">
+        <v>208.5</v>
+      </c>
+      <c r="C119" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="20">
+        <v>0</v>
+      </c>
+      <c r="E119" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G119" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="I119">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="9:9">
+    <row r="120" spans="1:9" ht="25">
+      <c r="A120" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B120">
+        <v>208.5</v>
+      </c>
+      <c r="C120" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" s="20">
+        <v>8</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F120">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G120" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="I120">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="9:9">
+    <row r="121" spans="1:9" ht="25">
+      <c r="A121" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B121">
+        <v>212.2</v>
+      </c>
+      <c r="C121" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D121" s="20">
+        <v>8</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G121" s="22" t="s">
+        <v>47</v>
+      </c>
       <c r="I121">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="9:9">
+    <row r="122" spans="1:9" ht="25">
+      <c r="A122" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B122">
+        <v>239.9</v>
+      </c>
+      <c r="C122" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" s="20">
+        <v>0</v>
+      </c>
+      <c r="E122" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="G122" s="22" t="s">
+        <v>50</v>
+      </c>
       <c r="I122">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="9:9">
+    <row r="123" spans="1:9" ht="25">
+      <c r="A123" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B123">
+        <v>239.9</v>
+      </c>
+      <c r="C123" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="20">
+        <v>8</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="G123" s="22" t="s">
+        <v>50</v>
+      </c>
       <c r="I123">
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="9:9">
+    <row r="124" spans="1:9" ht="25">
+      <c r="A124" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B124">
+        <v>229.2</v>
+      </c>
+      <c r="C124" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="20">
+        <v>0</v>
+      </c>
+      <c r="E124" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F124">
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="G124" s="22" t="s">
+        <v>51</v>
+      </c>
       <c r="I124">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="9:9">
+    <row r="125" spans="1:9" ht="25">
+      <c r="A125" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B125">
+        <v>239.9</v>
+      </c>
+      <c r="C125" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="20">
+        <v>8</v>
+      </c>
+      <c r="E125" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F125">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="G125" s="22" t="s">
+        <v>50</v>
+      </c>
       <c r="I125">
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="9:9">
+    <row r="126" spans="1:9" ht="25">
+      <c r="A126" s="1">
+        <v>42041</v>
+      </c>
+      <c r="B126">
+        <v>213.7</v>
+      </c>
+      <c r="C126" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D126" s="20">
+        <v>8</v>
+      </c>
+      <c r="E126" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G126" s="22" t="s">
+        <v>49</v>
+      </c>
       <c r="I126">
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="9:9">
+    <row r="127" spans="1:9" ht="25">
+      <c r="A127" s="1">
+        <v>42042</v>
+      </c>
+      <c r="B127">
+        <v>232.5</v>
+      </c>
+      <c r="C127" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="20">
+        <v>0</v>
+      </c>
+      <c r="E127" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127">
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="G127" s="22" t="s">
+        <v>52</v>
+      </c>
       <c r="I127">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="9:9">
+    <row r="128" spans="1:9" ht="25">
+      <c r="A128" s="1">
+        <v>42042</v>
+      </c>
+      <c r="B128">
+        <v>188.4</v>
+      </c>
+      <c r="C128" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="20">
+        <v>8</v>
+      </c>
+      <c r="E128" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="G128" s="22" t="s">
+        <v>53</v>
+      </c>
       <c r="I128">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="9:9">
+    <row r="129" spans="1:9" ht="25">
+      <c r="A129" s="1">
+        <v>42042</v>
+      </c>
+      <c r="B129">
+        <v>232.5</v>
+      </c>
+      <c r="C129" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="20">
+        <v>0</v>
+      </c>
+      <c r="E129" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F129">
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="G129" s="22" t="s">
+        <v>52</v>
+      </c>
       <c r="I129">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="9:9">
+    <row r="130" spans="1:9" ht="25">
+      <c r="A130" s="1">
+        <v>42042</v>
+      </c>
+      <c r="B130">
+        <v>188.4</v>
+      </c>
+      <c r="C130" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" s="20">
+        <v>8</v>
+      </c>
+      <c r="E130" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F130">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="G130" s="22" t="s">
+        <v>53</v>
+      </c>
       <c r="I130">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="9:9">
+    <row r="131" spans="1:9" ht="25">
+      <c r="A131" s="1">
+        <v>42042</v>
+      </c>
+      <c r="B131">
+        <v>244</v>
+      </c>
+      <c r="C131" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" s="20">
+        <v>8</v>
+      </c>
+      <c r="E131" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F131">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="G131" s="22" t="s">
+        <v>54</v>
+      </c>
       <c r="I131">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="9:9">
+    <row r="132" spans="1:9" ht="25">
+      <c r="A132" s="1">
+        <v>42042</v>
+      </c>
+      <c r="B132">
+        <v>248.9</v>
+      </c>
+      <c r="C132" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D132" s="20">
+        <v>8</v>
+      </c>
+      <c r="E132" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132">
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="G132" s="22" t="s">
+        <v>55</v>
+      </c>
       <c r="I132">
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="9:9">
+    <row r="133" spans="1:9" ht="25">
+      <c r="A133" s="1">
+        <v>42043</v>
+      </c>
+      <c r="B133">
+        <v>159.4</v>
+      </c>
+      <c r="C133" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" s="20">
+        <v>0</v>
+      </c>
+      <c r="E133" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="G133" s="22" t="s">
+        <v>60</v>
+      </c>
       <c r="I133">
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="9:9">
+    <row r="134" spans="1:9" ht="25">
+      <c r="A134" s="1">
+        <v>42043</v>
+      </c>
+      <c r="B134">
+        <v>159.4</v>
+      </c>
+      <c r="C134" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="20">
+        <v>8</v>
+      </c>
+      <c r="E134" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F134">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="G134" s="22" t="s">
+        <v>60</v>
+      </c>
       <c r="I134">
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="9:9">
+    <row r="135" spans="1:9" ht="25">
+      <c r="A135" s="1">
+        <v>42043</v>
+      </c>
+      <c r="B135">
+        <v>159.4</v>
+      </c>
+      <c r="C135" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" s="20">
+        <v>0</v>
+      </c>
+      <c r="E135" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F135">
+        <f t="shared" si="4"/>
+        <v>160</v>
+      </c>
+      <c r="G135" s="22" t="s">
+        <v>60</v>
+      </c>
       <c r="I135">
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="9:9">
+    <row r="136" spans="1:9" ht="25">
+      <c r="A136" s="1">
+        <v>42043</v>
+      </c>
+      <c r="B136">
+        <v>187.1</v>
+      </c>
+      <c r="C136" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" s="20">
+        <v>8</v>
+      </c>
+      <c r="E136" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="G136" s="22" t="s">
+        <v>59</v>
+      </c>
       <c r="I136">
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="9:9">
+    <row r="137" spans="1:9" ht="25">
+      <c r="A137" s="1">
+        <v>42043</v>
+      </c>
+      <c r="B137">
+        <v>194.6</v>
+      </c>
+      <c r="C137" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D137" s="20">
+        <v>8</v>
+      </c>
+      <c r="E137" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F137">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="G137" s="22" t="s">
+        <v>58</v>
+      </c>
       <c r="I137">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="9:9">
+    <row r="138" spans="1:9" ht="25">
+      <c r="A138" s="1">
+        <v>42043</v>
+      </c>
+      <c r="B138">
+        <v>176.7</v>
+      </c>
+      <c r="C138" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D138" s="20">
+        <v>8</v>
+      </c>
+      <c r="E138" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F138">
+        <f t="shared" si="4"/>
+        <v>180</v>
+      </c>
+      <c r="G138" s="22" t="s">
+        <v>57</v>
+      </c>
       <c r="I138">
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="9:9">
+    <row r="139" spans="1:9" ht="25">
+      <c r="A139" s="1">
+        <v>42044</v>
+      </c>
+      <c r="B139">
+        <v>210.6</v>
+      </c>
+      <c r="C139" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" s="20">
+        <v>0</v>
+      </c>
+      <c r="E139" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F139">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G139" s="22" t="s">
+        <v>62</v>
+      </c>
       <c r="I139">
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="9:9">
+    <row r="140" spans="1:9" ht="25">
+      <c r="A140" s="1">
+        <v>42044</v>
+      </c>
+      <c r="B140">
+        <v>203.9</v>
+      </c>
+      <c r="C140" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" s="20">
+        <v>8</v>
+      </c>
+      <c r="E140" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F140">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="G140" s="22" t="s">
+        <v>63</v>
+      </c>
       <c r="I140">
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="9:9">
+    <row r="141" spans="1:9" ht="25">
+      <c r="A141" s="1">
+        <v>42044</v>
+      </c>
+      <c r="B141">
+        <v>221.5</v>
+      </c>
+      <c r="C141" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="20">
+        <v>0</v>
+      </c>
+      <c r="E141" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F141">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G141" s="22" t="s">
+        <v>61</v>
+      </c>
       <c r="I141">
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="9:9">
+    <row r="142" spans="1:9" ht="25">
+      <c r="A142" s="1">
+        <v>42044</v>
+      </c>
+      <c r="B142">
+        <v>221.5</v>
+      </c>
+      <c r="C142" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" s="20">
+        <v>8</v>
+      </c>
+      <c r="E142" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F142">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G142" s="22" t="s">
+        <v>61</v>
+      </c>
       <c r="I142">
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="9:9">
+    <row r="143" spans="1:9" ht="25">
+      <c r="A143" s="1">
+        <v>42044</v>
+      </c>
+      <c r="B143">
+        <v>218.5</v>
+      </c>
+      <c r="C143" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D143" s="20">
+        <v>8</v>
+      </c>
+      <c r="E143" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F143">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G143" s="22" t="s">
+        <v>64</v>
+      </c>
       <c r="I143">
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="9:9">
+    <row r="144" spans="1:9" ht="25">
+      <c r="A144" s="1">
+        <v>42044</v>
+      </c>
+      <c r="B144">
+        <v>199.8</v>
+      </c>
+      <c r="C144" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D144" s="20">
+        <v>8</v>
+      </c>
+      <c r="E144" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="G144" s="22" t="s">
+        <v>65</v>
+      </c>
       <c r="I144">
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="9:9">
+    <row r="145" spans="1:9" ht="25">
+      <c r="A145" s="1">
+        <v>42046</v>
+      </c>
+      <c r="B145">
+        <v>205.5</v>
+      </c>
+      <c r="C145" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="20">
+        <v>0</v>
+      </c>
+      <c r="E145" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F145">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G145" s="22" t="s">
+        <v>69</v>
+      </c>
       <c r="I145">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="9:9">
+    <row r="146" spans="1:9" ht="25">
+      <c r="A146" s="1">
+        <v>42046</v>
+      </c>
+      <c r="B146">
+        <v>222</v>
+      </c>
+      <c r="C146" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="20">
+        <v>8</v>
+      </c>
+      <c r="E146" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F146">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G146" s="22" t="s">
+        <v>68</v>
+      </c>
       <c r="I146">
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="9:9">
+    <row r="147" spans="1:9" ht="25">
+      <c r="A147" s="1">
+        <v>42046</v>
+      </c>
+      <c r="B147">
+        <v>203.3</v>
+      </c>
+      <c r="C147" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D147" s="20">
+        <v>8</v>
+      </c>
+      <c r="E147" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F147">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="G147" s="22" t="s">
+        <v>67</v>
+      </c>
       <c r="I147">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="9:9">
+    <row r="148" spans="1:9" ht="25">
+      <c r="A148" s="1">
+        <v>42046</v>
+      </c>
+      <c r="B148">
+        <v>219.4</v>
+      </c>
+      <c r="C148" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D148" s="20">
+        <v>8</v>
+      </c>
+      <c r="E148" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F148">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G148" s="22" t="s">
+        <v>66</v>
+      </c>
       <c r="I148">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="9:9">
+    <row r="149" spans="1:9" ht="25">
+      <c r="A149" s="1">
+        <v>42047</v>
+      </c>
+      <c r="C149" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="20">
+        <v>0</v>
+      </c>
+      <c r="E149" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149" s="22" t="s">
+        <v>72</v>
+      </c>
       <c r="I149">
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="9:9">
+    <row r="150" spans="1:9" ht="25">
+      <c r="A150" s="1">
+        <v>42047</v>
+      </c>
+      <c r="C150" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="20">
+        <v>8</v>
+      </c>
+      <c r="E150" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" s="22" t="s">
+        <v>72</v>
+      </c>
       <c r="I150">
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="9:9">
+    <row r="151" spans="1:9" ht="25">
+      <c r="A151" s="1">
+        <v>42047</v>
+      </c>
+      <c r="C151" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D151" s="20">
+        <v>8</v>
+      </c>
+      <c r="E151" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G151" s="22" t="s">
+        <v>71</v>
+      </c>
       <c r="I151">
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="9:9">
+    <row r="152" spans="1:9" ht="25">
+      <c r="A152" s="1">
+        <v>42047</v>
+      </c>
+      <c r="C152" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D152" s="20">
+        <v>8</v>
+      </c>
+      <c r="E152" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" s="22" t="s">
+        <v>70</v>
+      </c>
       <c r="I152">
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="9:9">
+    <row r="153" spans="1:9">
       <c r="I153">
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="9:9">
+    <row r="154" spans="1:9">
       <c r="I154">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="9:9">
+    <row r="155" spans="1:9">
       <c r="I155">
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="9:9">
+    <row r="156" spans="1:9">
       <c r="I156">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="9:9">
+    <row r="157" spans="1:9">
       <c r="I157">
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="9:9">
+    <row r="158" spans="1:9">
       <c r="I158">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="9:9">
+    <row r="159" spans="1:9">
       <c r="I159">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="9:9">
+    <row r="160" spans="1:9">
       <c r="I160">
         <v>0</v>
       </c>

--- a/results.xlsx
+++ b/results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
   <workbookPr showInkAnnotation="0" hidePivotFieldList="1" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="1120" windowWidth="24480" windowHeight="14420" tabRatio="500" activeTab="2"/>
+    <workbookView xWindow="460" yWindow="0" windowWidth="23920" windowHeight="13860" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId4"/>
+    <pivotCache cacheId="61" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="148">
   <si>
     <t>Date</t>
   </si>
@@ -243,6 +243,231 @@
   </si>
   <si>
     <t>S135327370</t>
+  </si>
+  <si>
+    <t>S135633033</t>
+  </si>
+  <si>
+    <t>S135633222</t>
+  </si>
+  <si>
+    <t>S135633562</t>
+  </si>
+  <si>
+    <t>S135642884</t>
+  </si>
+  <si>
+    <t>S135643140</t>
+  </si>
+  <si>
+    <t>S135643352</t>
+  </si>
+  <si>
+    <t>S135643523</t>
+  </si>
+  <si>
+    <t>S135786416</t>
+  </si>
+  <si>
+    <t>S135789672</t>
+  </si>
+  <si>
+    <t>S135789902</t>
+  </si>
+  <si>
+    <t>S135790226</t>
+  </si>
+  <si>
+    <t>S135945102</t>
+  </si>
+  <si>
+    <t>S135945252</t>
+  </si>
+  <si>
+    <t>S135945398</t>
+  </si>
+  <si>
+    <t>S135945603</t>
+  </si>
+  <si>
+    <t>S136132688</t>
+  </si>
+  <si>
+    <t>S136132888</t>
+  </si>
+  <si>
+    <t>S136133205</t>
+  </si>
+  <si>
+    <t>S136133382</t>
+  </si>
+  <si>
+    <t>S136335267</t>
+  </si>
+  <si>
+    <t>S136335373</t>
+  </si>
+  <si>
+    <t>S136555674</t>
+  </si>
+  <si>
+    <t>S136556105</t>
+  </si>
+  <si>
+    <t>S136556625</t>
+  </si>
+  <si>
+    <t>S136557018</t>
+  </si>
+  <si>
+    <t>S137216050</t>
+  </si>
+  <si>
+    <t>S137217925</t>
+  </si>
+  <si>
+    <t>S137219413</t>
+  </si>
+  <si>
+    <t>S137220812</t>
+  </si>
+  <si>
+    <t>S137813258</t>
+  </si>
+  <si>
+    <t>S137815124</t>
+  </si>
+  <si>
+    <t>S137816030</t>
+  </si>
+  <si>
+    <t>S137816721</t>
+  </si>
+  <si>
+    <t>S138054611</t>
+  </si>
+  <si>
+    <t>S138055001</t>
+  </si>
+  <si>
+    <t>S138055299</t>
+  </si>
+  <si>
+    <t>S138058281</t>
+  </si>
+  <si>
+    <t>S138058773</t>
+  </si>
+  <si>
+    <t>S138661867</t>
+  </si>
+  <si>
+    <t>S138662412</t>
+  </si>
+  <si>
+    <t>S138662833</t>
+  </si>
+  <si>
+    <t>S138663125</t>
+  </si>
+  <si>
+    <t>S139226573</t>
+  </si>
+  <si>
+    <t>S139227064</t>
+  </si>
+  <si>
+    <t>S139227520</t>
+  </si>
+  <si>
+    <t>S139786602</t>
+  </si>
+  <si>
+    <t>S139787499</t>
+  </si>
+  <si>
+    <t>S139787999</t>
+  </si>
+  <si>
+    <t>S139789020</t>
+  </si>
+  <si>
+    <t>S140434070</t>
+  </si>
+  <si>
+    <t>S140435728</t>
+  </si>
+  <si>
+    <t>S140436227</t>
+  </si>
+  <si>
+    <t>S140436647</t>
+  </si>
+  <si>
+    <t>S141472840</t>
+  </si>
+  <si>
+    <t>S141473050</t>
+  </si>
+  <si>
+    <t>S141473151</t>
+  </si>
+  <si>
+    <t>S141666776</t>
+  </si>
+  <si>
+    <t>S141669238</t>
+  </si>
+  <si>
+    <t>S141671781</t>
+  </si>
+  <si>
+    <t>S142232876</t>
+  </si>
+  <si>
+    <t>S142234181</t>
+  </si>
+  <si>
+    <t>S142235128</t>
+  </si>
+  <si>
+    <t>S142235844</t>
+  </si>
+  <si>
+    <t>S142506186</t>
+  </si>
+  <si>
+    <t>S142508476</t>
+  </si>
+  <si>
+    <t>S142738865</t>
+  </si>
+  <si>
+    <t>S142739177</t>
+  </si>
+  <si>
+    <t>S143277009</t>
+  </si>
+  <si>
+    <t>S143277516</t>
+  </si>
+  <si>
+    <t>S143278956</t>
+  </si>
+  <si>
+    <t>S143279379</t>
+  </si>
+  <si>
+    <t>S143907915</t>
+  </si>
+  <si>
+    <t>S143908791</t>
+  </si>
+  <si>
+    <t>S143909226</t>
+  </si>
+  <si>
+    <t>S143909636</t>
   </si>
 </sst>
 </file>
@@ -286,7 +511,7 @@
       <name val="Helvetica"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,6 +554,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -354,7 +585,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="162">
+  <cellStyleXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -517,8 +748,95 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -544,11 +862,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="162">
+  <cellStyles count="249">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -630,6 +949,60 @@
     <cellStyle name="Followed Hyperlink" xfId="157" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="159" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="161" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="163" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="165" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="167" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="169" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="171" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="173" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="175" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="177" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="179" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="181" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="183" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="185" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="187" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="189" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="191" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="193" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="195" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="197" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="199" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="201" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="203" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="205" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="207" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="209" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="211" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="213" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="215" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="217" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="219" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="221" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="223" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="225" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="227" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="228" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="229" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="230" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="231" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="232" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="233" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="234" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="235" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="236" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="237" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="238" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="239" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="240" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="241" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="242" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="243" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="244" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="245" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="246" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="247" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="248" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -710,6 +1083,39 @@
     <cellStyle name="Hyperlink" xfId="156" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="158" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="160" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="162" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="164" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="166" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="168" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="170" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="172" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="174" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="176" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="178" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="180" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="182" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="184" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="186" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="188" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="190" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="192" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="194" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="196" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="198" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="200" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="202" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="204" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="206" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="208" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="210" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="212" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="214" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="216" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="218" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="220" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="222" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="224" builtinId="8" hidden="1"/>
+    <cellStyle name="Hyperlink" xfId="226" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -803,43 +1209,43 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>1.0</c:v>
+                  <c:v>4.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>7.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>41.0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>36.0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18.0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>17.0</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>5.0</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6.0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>19.0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6.0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>28.0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20.0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>13.0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>11.0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>14.0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>3.0</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.0</c:v>
+                  <c:v>10.0</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2.0</c:v>
@@ -860,8 +1266,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="-2125646632"/>
-        <c:axId val="-2125738872"/>
+        <c:axId val="-2112807896"/>
+        <c:axId val="-2112811192"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -933,49 +1339,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.00113936331686994</c:v>
+                  <c:v>0.001232257656464</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00223901419611758</c:v>
+                  <c:v>0.00247717835128003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.00394603925093226</c:v>
+                  <c:v>0.00442119653601064</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00623700214952315</c:v>
+                  <c:v>0.00700566168510025</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00884097832545786</c:v>
+                  <c:v>0.00985565051328814</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0112391818255554</c:v>
+                  <c:v>0.0123097213847046</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.012813831471045</c:v>
+                  <c:v>0.0136501664233175</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0131018691457743</c:v>
+                  <c:v>0.0134386135061302</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.012014271630392</c:v>
+                  <c:v>0.0117462104015132</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.00988033283984121</c:v>
+                  <c:v>0.00911523526280455</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.00728711532168424</c:v>
+                  <c:v>0.00628007431684782</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.00482002897793604</c:v>
+                  <c:v>0.00384139068094988</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.00285925964781033</c:v>
+                  <c:v>0.00208611847027228</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.00152113402352969</c:v>
+                  <c:v>0.00100581070272385</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.00072575711948566</c:v>
+                  <c:v>0.000430546765929341</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -992,11 +1398,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="-2125732408"/>
-        <c:axId val="-2125741912"/>
+        <c:axId val="-2112817640"/>
+        <c:axId val="-2112814232"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-2125732408"/>
+        <c:axId val="-2112817640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1006,7 +1412,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2125741912"/>
+        <c:crossAx val="-2112814232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1014,9 +1420,10 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-2125741912"/>
+        <c:axId val="-2112814232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="0.015"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1025,14 +1432,15 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2125732408"/>
+        <c:crossAx val="-2112817640"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-2125738872"/>
+        <c:axId val="-2112811192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="45.0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -1040,12 +1448,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2125646632"/>
+        <c:crossAx val="-2112807896"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="-2125646632"/>
+        <c:axId val="-2112807896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1055,7 +1463,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2125738872"/>
+        <c:crossAx val="-2112811192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1065,7 +1473,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -1116,16 +1523,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Jesse Green" refreshedDate="42047.398584490744" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="147">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Jesse Green" refreshedDate="42066.385978819446" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="235">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F148" sheet="Sheet4"/>
+    <worksheetSource ref="A1:F236" sheet="Sheet4"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2014-01-25T00:00:00" maxDate="2015-02-12T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2014-01-25T00:00:00" maxDate="2015-03-03T00:00:00"/>
     </cacheField>
     <cacheField name="score" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="152.30000000000001" maxValue="291.10000000000002"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="150.5" maxValue="291.10000000000002"/>
     </cacheField>
     <cacheField name="model" numFmtId="0">
       <sharedItems/>
@@ -1165,7 +1572,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="147">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="235">
   <r>
     <d v="2015-01-15T00:00:00"/>
     <n v="235.4"/>
@@ -2341,12 +2748,716 @@
     <n v="8"/>
     <s v="l2"/>
     <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-12T00:00:00"/>
+    <n v="216.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-12T00:00:00"/>
+    <n v="216.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-12T00:00:00"/>
+    <n v="166.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-02-12T00:00:00"/>
+    <n v="168"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-02-14T00:00:00"/>
+    <n v="195.1"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-14T00:00:00"/>
+    <n v="222.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-14T00:00:00"/>
+    <n v="205"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-14T00:00:00"/>
+    <n v="222.4"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-14T00:00:00"/>
+    <n v="200"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-14T00:00:00"/>
+    <n v="234.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-14T00:00:00"/>
+    <n v="222.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-14T00:00:00"/>
+    <n v="220.9"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-15T00:00:00"/>
+    <n v="235"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-15T00:00:00"/>
+    <n v="235"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-15T00:00:00"/>
+    <n v="235"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-15T00:00:00"/>
+    <n v="235"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-15T00:00:00"/>
+    <n v="252.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-15T00:00:00"/>
+    <n v="212.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-15T00:00:00"/>
+    <n v="222.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-15T00:00:00"/>
+    <n v="212.7"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-16T00:00:00"/>
+    <n v="183.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-02-16T00:00:00"/>
+    <n v="213.2"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-16T00:00:00"/>
+    <n v="177.7"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-02-16T00:00:00"/>
+    <n v="190.8"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-17T00:00:00"/>
+    <n v="150.69999999999999"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <d v="2015-02-17T00:00:00"/>
+    <n v="176.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-02-17T00:00:00"/>
+    <n v="150.5"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <d v="2015-02-17T00:00:00"/>
+    <n v="191"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-18T00:00:00"/>
+    <n v="235.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-18T00:00:00"/>
+    <n v="226.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-18T00:00:00"/>
+    <n v="226.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-18T00:00:00"/>
+    <n v="226.9"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-19T00:00:00"/>
+    <n v="176.1"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-02-19T00:00:00"/>
+    <n v="219.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-19T00:00:00"/>
+    <n v="197.2"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-19T00:00:00"/>
+    <n v="221"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-20T00:00:00"/>
+    <n v="211.3"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-20T00:00:00"/>
+    <n v="269"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-02-20T00:00:00"/>
+    <n v="228"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-20T00:00:00"/>
+    <n v="250.8"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-20T00:00:00"/>
+    <n v="168.3"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-02-20T00:00:00"/>
+    <n v="152.80000000000001"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <d v="2015-02-20T00:00:00"/>
+    <n v="158.1"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <d v="2015-02-20T00:00:00"/>
+    <n v="175.8"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-02-21T00:00:00"/>
+    <n v="216.5"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-21T00:00:00"/>
+    <n v="216.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-21T00:00:00"/>
+    <n v="238.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-02-21T00:00:00"/>
+    <n v="256.7"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <d v="2015-02-21T00:00:00"/>
+    <n v="231.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-21T00:00:00"/>
+    <n v="231.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-21T00:00:00"/>
+    <n v="208.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-21T00:00:00"/>
+    <n v="231.9"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-22T00:00:00"/>
+    <n v="207.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-22T00:00:00"/>
+    <n v="188.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-22T00:00:00"/>
+    <n v="205.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-22T00:00:00"/>
+    <n v="189"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-23T00:00:00"/>
+    <n v="200.7"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-23T00:00:00"/>
+    <n v="200.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-02-23T00:00:00"/>
+    <n v="158.1"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <d v="2015-02-23T00:00:00"/>
+    <n v="212.7"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-24T00:00:00"/>
+    <n v="218.3"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-24T00:00:00"/>
+    <n v="231.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-24T00:00:00"/>
+    <n v="246.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-02-24T00:00:00"/>
+    <n v="218.5"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-25T00:00:00"/>
+    <n v="221"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-25T00:00:00"/>
+    <n v="188"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-25T00:00:00"/>
+    <n v="209.1"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-25T00:00:00"/>
+    <n v="192"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-02-27T00:00:00"/>
+    <n v="171.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-02-27T00:00:00"/>
+    <n v="171.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-02-27T00:00:00"/>
+    <n v="174.2"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-02-27T00:00:00"/>
+    <n v="184.7"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-02-28T00:00:00"/>
+    <n v="228.1"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-02-28T00:00:00"/>
+    <n v="206.5"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-02-28T00:00:00"/>
+    <n v="221.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-02-28T00:00:00"/>
+    <n v="221.9"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-01T00:00:00"/>
+    <n v="235.7"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-03-01T00:00:00"/>
+    <n v="205.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-03-01T00:00:00"/>
+    <n v="257.2"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <d v="2015-03-01T00:00:00"/>
+    <n v="206"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-03-01T00:00:00"/>
+    <n v="202.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-01T00:00:00"/>
+    <n v="202.2"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-01T00:00:00"/>
+    <n v="185.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-03-01T00:00:00"/>
+    <n v="202.2"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-02T00:00:00"/>
+    <n v="202.1"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-02T00:00:00"/>
+    <n v="202.1"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-02T00:00:00"/>
+    <n v="197.4"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-02T00:00:00"/>
+    <n v="202.1"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:B20" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField numFmtId="14" showAll="0"/>
@@ -2773,26 +3884,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="53" customHeight="1">
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23" t="s">
+      <c r="C1" s="24"/>
+      <c r="D1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23" t="s">
+      <c r="E1" s="24"/>
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23" t="s">
+      <c r="G1" s="24"/>
+      <c r="H1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23" t="s">
+      <c r="I1" s="24"/>
+      <c r="J1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="23"/>
+      <c r="K1" s="24"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" t="s">
@@ -3497,7 +4608,7 @@
       </c>
       <c r="W3">
         <f>_xlfn.NORM.DIST(V3,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.1393633168699394E-3</v>
+        <v>1.2322576564640026E-3</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -3512,7 +4623,7 @@
       </c>
       <c r="W4">
         <f>_xlfn.NORM.DIST(V4,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>2.2390141961175767E-3</v>
+        <v>2.4771783512800303E-3</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -3520,14 +4631,14 @@
         <v>150</v>
       </c>
       <c r="B5" s="18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V5">
         <v>170</v>
       </c>
       <c r="W5">
         <f>_xlfn.NORM.DIST(V5,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>3.9460392509322595E-3</v>
+        <v>4.4211965360106409E-3</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -3535,14 +4646,14 @@
         <v>160</v>
       </c>
       <c r="B6" s="18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>180</v>
       </c>
       <c r="W6">
         <f>_xlfn.NORM.DIST(V6,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>6.2370021495231475E-3</v>
+        <v>7.0056616851002533E-3</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -3550,14 +4661,14 @@
         <v>170</v>
       </c>
       <c r="B7" s="18">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V7">
         <v>190</v>
       </c>
       <c r="W7">
         <f>_xlfn.NORM.DIST(V7,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>8.8409783254578614E-3</v>
+        <v>9.8556505132881399E-3</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -3565,14 +4676,14 @@
         <v>180</v>
       </c>
       <c r="B8" s="18">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="V8">
         <v>200</v>
       </c>
       <c r="W8">
         <f>_xlfn.NORM.DIST(V8,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.1239181825555446E-2</v>
+        <v>1.2309721384704569E-2</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -3580,14 +4691,14 @@
         <v>190</v>
       </c>
       <c r="B9" s="18">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="V9">
         <v>210</v>
       </c>
       <c r="W9">
         <f>_xlfn.NORM.DIST(V9,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.2813831471045038E-2</v>
+        <v>1.3650166423317553E-2</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -3595,14 +4706,14 @@
         <v>200</v>
       </c>
       <c r="B10" s="18">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="V10">
         <v>220</v>
       </c>
       <c r="W10">
         <f>_xlfn.NORM.DIST(V10,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.3101869145774273E-2</v>
+        <v>1.3438613506130237E-2</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -3610,14 +4721,14 @@
         <v>210</v>
       </c>
       <c r="B11" s="18">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="V11">
         <v>230</v>
       </c>
       <c r="W11">
         <f>_xlfn.NORM.DIST(V11,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.2014271630391963E-2</v>
+        <v>1.1746210401513217E-2</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -3625,14 +4736,14 @@
         <v>220</v>
       </c>
       <c r="B12" s="18">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="V12">
         <v>240</v>
       </c>
       <c r="W12">
         <f>_xlfn.NORM.DIST(V12,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>9.8803328398412143E-3</v>
+        <v>9.1152352628045517E-3</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -3640,14 +4751,14 @@
         <v>230</v>
       </c>
       <c r="B13" s="18">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="V13">
         <v>250</v>
       </c>
       <c r="W13">
         <f>_xlfn.NORM.DIST(V13,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>7.2871153216842394E-3</v>
+        <v>6.2800743168478241E-3</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -3655,14 +4766,14 @@
         <v>240</v>
       </c>
       <c r="B14" s="18">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V14">
         <v>260</v>
       </c>
       <c r="W14">
         <f>_xlfn.NORM.DIST(V14,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>4.8200289779360391E-3</v>
+        <v>3.8413906809498812E-3</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -3670,14 +4781,14 @@
         <v>250</v>
       </c>
       <c r="B15" s="18">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V15">
         <v>270</v>
       </c>
       <c r="W15">
         <f>_xlfn.NORM.DIST(V15,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>2.8592596478103334E-3</v>
+        <v>2.0861184702722761E-3</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -3685,14 +4796,14 @@
         <v>260</v>
       </c>
       <c r="B16" s="18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>280</v>
       </c>
       <c r="W16">
         <f>_xlfn.NORM.DIST(V16,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.5211340235296864E-3</v>
+        <v>1.0058107027238546E-3</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -3700,14 +4811,14 @@
         <v>270</v>
       </c>
       <c r="B17" s="18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>290</v>
       </c>
       <c r="W17">
         <f>_xlfn.NORM.DIST(V17,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>7.2575711948566013E-4</v>
+        <v>4.3054676592934135E-4</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -3731,7 +4842,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="18">
-        <v>147</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3747,8 +4858,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J200"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <dimension ref="A1:J1048576"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="7" max="7" width="24.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
@@ -3802,7 +4913,7 @@
       </c>
       <c r="J2">
         <f>AVERAGE(B:B)</f>
-        <v>217.04149659863958</v>
+        <v>213.68723404255331</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="18">
@@ -3830,7 +4941,7 @@
       </c>
       <c r="J3">
         <f>_xlfn.STDEV.S(B:B)</f>
-        <v>30.304506748198964</v>
+        <v>28.99075019756452</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="18">
@@ -6370,7 +7481,7 @@
         <v>19</v>
       </c>
       <c r="F106">
-        <f t="shared" ref="F106:F148" si="4">ROUND(B106/10,0)*10</f>
+        <f t="shared" ref="F106:F169" si="4">ROUND(B106/10,0)*10</f>
         <v>290</v>
       </c>
       <c r="G106" s="22" t="s">
@@ -7518,6 +8629,9 @@
       <c r="A149" s="1">
         <v>42047</v>
       </c>
+      <c r="B149">
+        <v>216.5</v>
+      </c>
       <c r="C149" s="20" t="s">
         <v>12</v>
       </c>
@@ -7526,6 +8640,10 @@
       </c>
       <c r="E149" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F149">
+        <f t="shared" si="4"/>
+        <v>220</v>
       </c>
       <c r="G149" s="22" t="s">
         <v>72</v>
@@ -7538,6 +8656,9 @@
       <c r="A150" s="1">
         <v>42047</v>
       </c>
+      <c r="B150">
+        <v>216.5</v>
+      </c>
       <c r="C150" s="20" t="s">
         <v>12</v>
       </c>
@@ -7546,6 +8667,10 @@
       </c>
       <c r="E150" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F150">
+        <f t="shared" si="4"/>
+        <v>220</v>
       </c>
       <c r="G150" s="22" t="s">
         <v>72</v>
@@ -7558,6 +8683,9 @@
       <c r="A151" s="1">
         <v>42047</v>
       </c>
+      <c r="B151">
+        <v>166.3</v>
+      </c>
       <c r="C151" s="20" t="s">
         <v>20</v>
       </c>
@@ -7566,6 +8694,10 @@
       </c>
       <c r="E151" s="19" t="s">
         <v>19</v>
+      </c>
+      <c r="F151">
+        <f t="shared" si="4"/>
+        <v>170</v>
       </c>
       <c r="G151" s="22" t="s">
         <v>71</v>
@@ -7578,6 +8710,9 @@
       <c r="A152" s="1">
         <v>42047</v>
       </c>
+      <c r="B152">
+        <v>168</v>
+      </c>
       <c r="C152" s="20" t="s">
         <v>56</v>
       </c>
@@ -7587,6 +8722,10 @@
       <c r="E152" s="19" t="s">
         <v>13</v>
       </c>
+      <c r="F152">
+        <f t="shared" si="4"/>
+        <v>170</v>
+      </c>
       <c r="G152" s="22" t="s">
         <v>70</v>
       </c>
@@ -7594,247 +8733,2311 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" ht="25">
+      <c r="A153" s="1">
+        <v>42049</v>
+      </c>
+      <c r="B153">
+        <v>195.1</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="20">
+        <v>0</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F153">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="G153" s="22" t="s">
+        <v>73</v>
+      </c>
       <c r="I153">
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" ht="25">
+      <c r="A154" s="1">
+        <v>42049</v>
+      </c>
+      <c r="B154">
+        <v>222.4</v>
+      </c>
+      <c r="C154" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" s="20">
+        <v>8</v>
+      </c>
+      <c r="E154" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G154" s="22" t="s">
+        <v>74</v>
+      </c>
       <c r="I154">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" ht="25">
+      <c r="A155" s="1">
+        <v>42049</v>
+      </c>
+      <c r="B155">
+        <v>205</v>
+      </c>
+      <c r="C155" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D155" s="20">
+        <v>8</v>
+      </c>
+      <c r="E155" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F155">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G155" s="22" t="s">
+        <v>75</v>
+      </c>
       <c r="I155">
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" ht="25">
+      <c r="A156" s="1">
+        <v>42049</v>
+      </c>
+      <c r="B156">
+        <v>222.4</v>
+      </c>
+      <c r="C156" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D156" s="20">
+        <v>8</v>
+      </c>
+      <c r="E156" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G156" s="22" t="s">
+        <v>74</v>
+      </c>
       <c r="I156">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" ht="25">
+      <c r="A157" s="1">
+        <v>42049</v>
+      </c>
+      <c r="B157">
+        <v>200</v>
+      </c>
+      <c r="C157" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D157" s="20">
+        <v>0</v>
+      </c>
+      <c r="E157" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="G157" s="22" t="s">
+        <v>76</v>
+      </c>
       <c r="I157">
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" ht="25">
+      <c r="A158" s="1">
+        <v>42049</v>
+      </c>
+      <c r="B158">
+        <v>234.8</v>
+      </c>
+      <c r="C158" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158" s="20">
+        <v>8</v>
+      </c>
+      <c r="E158" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158">
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="G158" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="I158">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" ht="25">
+      <c r="A159" s="1">
+        <v>42049</v>
+      </c>
+      <c r="B159">
+        <v>222.3</v>
+      </c>
+      <c r="C159" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D159" s="20">
+        <v>8</v>
+      </c>
+      <c r="E159" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F159">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G159" s="22" t="s">
+        <v>78</v>
+      </c>
       <c r="I159">
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" ht="25">
+      <c r="A160" s="1">
+        <v>42049</v>
+      </c>
+      <c r="B160">
+        <v>220.9</v>
+      </c>
+      <c r="C160" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D160" s="20">
+        <v>8</v>
+      </c>
+      <c r="E160" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G160" s="22" t="s">
+        <v>79</v>
+      </c>
       <c r="I160">
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="9:9">
+    <row r="161" spans="1:9" ht="25">
+      <c r="A161" s="1">
+        <v>42050</v>
+      </c>
+      <c r="B161">
+        <v>235</v>
+      </c>
+      <c r="C161" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161" s="20">
+        <v>0</v>
+      </c>
+      <c r="E161" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="G161" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="I161">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="9:9">
+    <row r="162" spans="1:9" ht="25">
+      <c r="A162" s="1">
+        <v>42050</v>
+      </c>
+      <c r="B162">
+        <v>235</v>
+      </c>
+      <c r="C162" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D162" s="20">
+        <v>8</v>
+      </c>
+      <c r="E162" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F162">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="G162" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="I162">
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="9:9">
+    <row r="163" spans="1:9" ht="25">
+      <c r="A163" s="1">
+        <v>42050</v>
+      </c>
+      <c r="B163">
+        <v>235</v>
+      </c>
+      <c r="C163" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D163" s="20">
+        <v>8</v>
+      </c>
+      <c r="E163" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F163">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="G163" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="I163">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="9:9">
+    <row r="164" spans="1:9" ht="25">
+      <c r="A164" s="1">
+        <v>42050</v>
+      </c>
+      <c r="B164">
+        <v>235</v>
+      </c>
+      <c r="C164" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D164" s="20">
+        <v>8</v>
+      </c>
+      <c r="E164" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F164">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="G164" s="22" t="s">
+        <v>80</v>
+      </c>
       <c r="I164">
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="9:9">
+    <row r="165" spans="1:9" ht="25">
+      <c r="A165" s="1">
+        <v>42050</v>
+      </c>
+      <c r="B165">
+        <v>252.4</v>
+      </c>
+      <c r="C165" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165" s="20">
+        <v>0</v>
+      </c>
+      <c r="E165" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165">
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="G165" s="22" t="s">
+        <v>82</v>
+      </c>
       <c r="I165">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="9:9">
+    <row r="166" spans="1:9" ht="25">
+      <c r="A166" s="1">
+        <v>42050</v>
+      </c>
+      <c r="B166">
+        <v>212.7</v>
+      </c>
+      <c r="C166" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D166" s="20">
+        <v>8</v>
+      </c>
+      <c r="E166" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F166">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G166" s="22" t="s">
+        <v>81</v>
+      </c>
       <c r="I166">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="9:9">
+    <row r="167" spans="1:9" ht="25">
+      <c r="A167" s="1">
+        <v>42050</v>
+      </c>
+      <c r="B167">
+        <v>222.9</v>
+      </c>
+      <c r="C167" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D167" s="20">
+        <v>8</v>
+      </c>
+      <c r="E167" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F167">
+        <f t="shared" si="4"/>
+        <v>220</v>
+      </c>
+      <c r="G167" s="22" t="s">
+        <v>83</v>
+      </c>
       <c r="I167">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="9:9">
+    <row r="168" spans="1:9" ht="25">
+      <c r="A168" s="1">
+        <v>42050</v>
+      </c>
+      <c r="B168">
+        <v>212.7</v>
+      </c>
+      <c r="C168" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D168" s="20">
+        <v>8</v>
+      </c>
+      <c r="E168" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G168" s="22" t="s">
+        <v>81</v>
+      </c>
       <c r="I168">
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="9:9">
+    <row r="169" spans="1:9" ht="25">
+      <c r="A169" s="1">
+        <v>42051</v>
+      </c>
+      <c r="B169">
+        <v>183.9</v>
+      </c>
+      <c r="C169" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="20">
+        <v>0</v>
+      </c>
+      <c r="E169" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169">
+        <f t="shared" si="4"/>
+        <v>180</v>
+      </c>
+      <c r="G169" s="22" t="s">
+        <v>84</v>
+      </c>
       <c r="I169">
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="9:9">
+    <row r="170" spans="1:9" ht="25">
+      <c r="A170" s="1">
+        <v>42051</v>
+      </c>
+      <c r="B170">
+        <v>213.2</v>
+      </c>
+      <c r="C170" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" s="20">
+        <v>8</v>
+      </c>
+      <c r="E170" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170">
+        <f t="shared" ref="F170:F233" si="5">ROUND(B170/10,0)*10</f>
+        <v>210</v>
+      </c>
+      <c r="G170" s="22" t="s">
+        <v>85</v>
+      </c>
       <c r="I170">
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="9:9">
+    <row r="171" spans="1:9" ht="25">
+      <c r="A171" s="1">
+        <v>42051</v>
+      </c>
+      <c r="B171">
+        <v>177.7</v>
+      </c>
+      <c r="C171" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D171" s="20">
+        <v>8</v>
+      </c>
+      <c r="E171" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F171">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="G171" s="22" t="s">
+        <v>86</v>
+      </c>
       <c r="I171">
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="9:9">
+    <row r="172" spans="1:9" ht="25">
+      <c r="A172" s="1">
+        <v>42051</v>
+      </c>
+      <c r="B172">
+        <v>190.8</v>
+      </c>
+      <c r="C172" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D172" s="20">
+        <v>8</v>
+      </c>
+      <c r="E172" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="G172" s="22" t="s">
+        <v>87</v>
+      </c>
       <c r="I172">
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="9:9">
+    <row r="173" spans="1:9" ht="25">
+      <c r="A173" s="1">
+        <v>42052</v>
+      </c>
+      <c r="B173">
+        <v>150.69999999999999</v>
+      </c>
+      <c r="C173" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" s="20">
+        <v>0</v>
+      </c>
+      <c r="E173" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173">
+        <f t="shared" si="5"/>
+        <v>150</v>
+      </c>
+      <c r="G173" s="22" t="s">
+        <v>88</v>
+      </c>
       <c r="I173">
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="9:9">
+    <row r="174" spans="1:9" ht="25">
+      <c r="A174" s="1">
+        <v>42052</v>
+      </c>
+      <c r="B174">
+        <v>176.9</v>
+      </c>
+      <c r="C174" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174" s="20">
+        <v>8</v>
+      </c>
+      <c r="E174" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="G174" s="22" t="s">
+        <v>89</v>
+      </c>
       <c r="I174">
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="9:9">
+    <row r="175" spans="1:9" ht="25">
+      <c r="A175" s="1">
+        <v>42052</v>
+      </c>
+      <c r="B175">
+        <v>150.5</v>
+      </c>
+      <c r="C175" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D175" s="20">
+        <v>8</v>
+      </c>
+      <c r="E175" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F175">
+        <f t="shared" si="5"/>
+        <v>150</v>
+      </c>
+      <c r="G175" s="22" t="s">
+        <v>90</v>
+      </c>
       <c r="I175">
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="9:9">
+    <row r="176" spans="1:9" ht="25">
+      <c r="A176" s="1">
+        <v>42052</v>
+      </c>
+      <c r="B176">
+        <v>191</v>
+      </c>
+      <c r="C176" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D176" s="20">
+        <v>8</v>
+      </c>
+      <c r="E176" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="G176" s="22" t="s">
+        <v>91</v>
+      </c>
       <c r="I176">
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="9:9">
+    <row r="177" spans="1:9" ht="25">
+      <c r="A177" s="1">
+        <v>42053</v>
+      </c>
+      <c r="B177">
+        <v>235.5</v>
+      </c>
+      <c r="C177" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D177" s="20">
+        <v>0</v>
+      </c>
+      <c r="E177" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177">
+        <f t="shared" si="5"/>
+        <v>240</v>
+      </c>
+      <c r="G177" s="22" t="s">
+        <v>92</v>
+      </c>
       <c r="I177">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="9:9">
+    <row r="178" spans="1:9" ht="25">
+      <c r="A178" s="1">
+        <v>42053</v>
+      </c>
+      <c r="B178">
+        <v>226.9</v>
+      </c>
+      <c r="C178" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178" s="20">
+        <v>8</v>
+      </c>
+      <c r="E178" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G178" s="22" t="s">
+        <v>93</v>
+      </c>
       <c r="I178">
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="9:9">
+    <row r="179" spans="1:9" ht="25">
+      <c r="A179" s="1">
+        <v>42053</v>
+      </c>
+      <c r="B179">
+        <v>226.9</v>
+      </c>
+      <c r="C179" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D179" s="20">
+        <v>8</v>
+      </c>
+      <c r="E179" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F179">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G179" s="22" t="s">
+        <v>93</v>
+      </c>
       <c r="I179">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="9:9">
+    <row r="180" spans="1:9" ht="25">
+      <c r="A180" s="1">
+        <v>42053</v>
+      </c>
+      <c r="B180">
+        <v>226.9</v>
+      </c>
+      <c r="C180" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D180" s="20">
+        <v>8</v>
+      </c>
+      <c r="E180" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F180">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G180" s="22" t="s">
+        <v>93</v>
+      </c>
       <c r="I180">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="9:9">
+    <row r="181" spans="1:9" ht="25">
+      <c r="A181" s="1">
+        <v>42054</v>
+      </c>
+      <c r="B181">
+        <v>176.1</v>
+      </c>
+      <c r="C181" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D181" s="20">
+        <v>0</v>
+      </c>
+      <c r="E181" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="G181" s="22" t="s">
+        <v>94</v>
+      </c>
       <c r="I181">
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="9:9">
+    <row r="182" spans="1:9" ht="25">
+      <c r="A182" s="1">
+        <v>42054</v>
+      </c>
+      <c r="B182">
+        <v>219.4</v>
+      </c>
+      <c r="C182" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D182" s="20">
+        <v>8</v>
+      </c>
+      <c r="E182" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G182" s="22" t="s">
+        <v>95</v>
+      </c>
       <c r="I182">
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="9:9">
+    <row r="183" spans="1:9" ht="25">
+      <c r="A183" s="1">
+        <v>42054</v>
+      </c>
+      <c r="B183">
+        <v>197.2</v>
+      </c>
+      <c r="C183" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D183" s="20">
+        <v>8</v>
+      </c>
+      <c r="E183" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F183">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="G183" s="22" t="s">
+        <v>96</v>
+      </c>
       <c r="I183">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="9:9">
+    <row r="184" spans="1:9" ht="25">
+      <c r="A184" s="1">
+        <v>42054</v>
+      </c>
+      <c r="B184">
+        <v>221</v>
+      </c>
+      <c r="C184" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D184" s="20">
+        <v>8</v>
+      </c>
+      <c r="E184" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G184" s="22" t="s">
+        <v>97</v>
+      </c>
       <c r="I184">
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="9:9">
+    <row r="185" spans="1:9" ht="25">
+      <c r="A185" s="1">
+        <v>42055</v>
+      </c>
+      <c r="B185">
+        <v>211.3</v>
+      </c>
+      <c r="C185" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" s="20">
+        <v>0</v>
+      </c>
+      <c r="E185" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G185" s="22" t="s">
+        <v>98</v>
+      </c>
       <c r="I185">
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="9:9">
+    <row r="186" spans="1:9" ht="25">
+      <c r="A186" s="1">
+        <v>42055</v>
+      </c>
+      <c r="B186">
+        <v>269</v>
+      </c>
+      <c r="C186" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D186" s="20">
+        <v>8</v>
+      </c>
+      <c r="E186" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186">
+        <f t="shared" si="5"/>
+        <v>270</v>
+      </c>
+      <c r="G186" s="22" t="s">
+        <v>99</v>
+      </c>
       <c r="I186">
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="9:9">
+    <row r="187" spans="1:9" ht="25">
+      <c r="A187" s="1">
+        <v>42055</v>
+      </c>
+      <c r="B187">
+        <v>228</v>
+      </c>
+      <c r="C187" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D187" s="20">
+        <v>8</v>
+      </c>
+      <c r="E187" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F187">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G187" s="22" t="s">
+        <v>100</v>
+      </c>
       <c r="I187">
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="9:9">
+    <row r="188" spans="1:9" ht="25">
+      <c r="A188" s="1">
+        <v>42055</v>
+      </c>
+      <c r="B188">
+        <v>250.8</v>
+      </c>
+      <c r="C188" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D188" s="20">
+        <v>8</v>
+      </c>
+      <c r="E188" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188">
+        <f t="shared" si="5"/>
+        <v>250</v>
+      </c>
+      <c r="G188" s="22" t="s">
+        <v>101</v>
+      </c>
       <c r="I188">
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="9:9">
+    <row r="189" spans="1:9" ht="25">
+      <c r="A189" s="1">
+        <v>42055</v>
+      </c>
+      <c r="B189">
+        <v>168.3</v>
+      </c>
+      <c r="C189" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D189" s="20">
+        <v>0</v>
+      </c>
+      <c r="E189" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189">
+        <f t="shared" si="5"/>
+        <v>170</v>
+      </c>
+      <c r="G189" s="22" t="s">
+        <v>102</v>
+      </c>
       <c r="I189">
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="9:9">
+    <row r="190" spans="1:9" ht="25">
+      <c r="A190" s="1">
+        <v>42055</v>
+      </c>
+      <c r="B190">
+        <v>152.80000000000001</v>
+      </c>
+      <c r="C190" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D190" s="20">
+        <v>8</v>
+      </c>
+      <c r="E190" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190">
+        <f t="shared" si="5"/>
+        <v>150</v>
+      </c>
+      <c r="G190" s="22" t="s">
+        <v>103</v>
+      </c>
       <c r="I190">
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="9:9">
+    <row r="191" spans="1:9" ht="25">
+      <c r="A191" s="1">
+        <v>42055</v>
+      </c>
+      <c r="B191">
+        <v>158.1</v>
+      </c>
+      <c r="C191" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D191" s="20">
+        <v>8</v>
+      </c>
+      <c r="E191" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F191">
+        <f t="shared" si="5"/>
+        <v>160</v>
+      </c>
+      <c r="G191" s="22" t="s">
+        <v>104</v>
+      </c>
       <c r="I191">
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="9:9">
+    <row r="192" spans="1:9" ht="25">
+      <c r="A192" s="1">
+        <v>42055</v>
+      </c>
+      <c r="B192">
+        <v>175.8</v>
+      </c>
+      <c r="C192" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D192" s="20">
+        <v>8</v>
+      </c>
+      <c r="E192" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="G192" s="22" t="s">
+        <v>105</v>
+      </c>
       <c r="I192">
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="9:9">
+    <row r="193" spans="1:9" ht="25">
+      <c r="A193" s="1">
+        <v>42056</v>
+      </c>
+      <c r="B193">
+        <v>216.5</v>
+      </c>
+      <c r="C193" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D193" s="20">
+        <v>0</v>
+      </c>
+      <c r="E193" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F193">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G193" s="22" t="s">
+        <v>106</v>
+      </c>
       <c r="I193">
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="9:9">
+    <row r="194" spans="1:9" ht="25">
+      <c r="A194" s="1">
+        <v>42056</v>
+      </c>
+      <c r="B194">
+        <v>216.5</v>
+      </c>
+      <c r="C194" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D194" s="20">
+        <v>8</v>
+      </c>
+      <c r="E194" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F194">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G194" s="22" t="s">
+        <v>106</v>
+      </c>
       <c r="I194">
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="9:9">
+    <row r="195" spans="1:9" ht="25">
+      <c r="A195" s="1">
+        <v>42056</v>
+      </c>
+      <c r="B195">
+        <v>238.3</v>
+      </c>
+      <c r="C195" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D195" s="20">
+        <v>8</v>
+      </c>
+      <c r="E195" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F195">
+        <f t="shared" si="5"/>
+        <v>240</v>
+      </c>
+      <c r="G195" s="22" t="s">
+        <v>107</v>
+      </c>
       <c r="I195">
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="9:9">
+    <row r="196" spans="1:9" ht="25">
+      <c r="A196" s="1">
+        <v>42056</v>
+      </c>
+      <c r="B196">
+        <v>256.7</v>
+      </c>
+      <c r="C196" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D196" s="20">
+        <v>8</v>
+      </c>
+      <c r="E196" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F196">
+        <f t="shared" si="5"/>
+        <v>260</v>
+      </c>
+      <c r="G196" s="22" t="s">
+        <v>108</v>
+      </c>
       <c r="I196">
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="9:9">
+    <row r="197" spans="1:9" ht="25">
+      <c r="A197" s="1">
+        <v>42056</v>
+      </c>
+      <c r="B197">
+        <v>231.9</v>
+      </c>
+      <c r="C197" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D197" s="20">
+        <v>0</v>
+      </c>
+      <c r="E197" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F197">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G197" s="22" t="s">
+        <v>109</v>
+      </c>
       <c r="I197">
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="9:9">
+    <row r="198" spans="1:9" ht="25">
+      <c r="A198" s="1">
+        <v>42056</v>
+      </c>
+      <c r="B198">
+        <v>231.9</v>
+      </c>
+      <c r="C198" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D198" s="20">
+        <v>8</v>
+      </c>
+      <c r="E198" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F198">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G198" s="22" t="s">
+        <v>109</v>
+      </c>
       <c r="I198">
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="9:9">
+    <row r="199" spans="1:9" ht="25">
+      <c r="A199" s="1">
+        <v>42056</v>
+      </c>
+      <c r="B199">
+        <v>208.9</v>
+      </c>
+      <c r="C199" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D199" s="20">
+        <v>8</v>
+      </c>
+      <c r="E199" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F199">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G199" s="22" t="s">
+        <v>110</v>
+      </c>
       <c r="I199">
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="9:9">
+    <row r="200" spans="1:9" ht="25">
+      <c r="A200" s="1">
+        <v>42056</v>
+      </c>
+      <c r="B200">
+        <v>231.9</v>
+      </c>
+      <c r="C200" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D200" s="20">
+        <v>8</v>
+      </c>
+      <c r="E200" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F200">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G200" s="22" t="s">
+        <v>109</v>
+      </c>
       <c r="I200">
         <v>0</v>
       </c>
     </row>
+    <row r="201" spans="1:9" ht="25">
+      <c r="A201" s="1">
+        <v>42057</v>
+      </c>
+      <c r="B201">
+        <v>207.9</v>
+      </c>
+      <c r="C201" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D201" s="20">
+        <v>0</v>
+      </c>
+      <c r="E201" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F201">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G201" s="22" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="25">
+      <c r="A202" s="1">
+        <v>42057</v>
+      </c>
+      <c r="B202">
+        <v>188.7</v>
+      </c>
+      <c r="C202" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D202" s="20">
+        <v>8</v>
+      </c>
+      <c r="E202" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F202">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="G202" s="22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="25">
+      <c r="A203" s="1">
+        <v>42057</v>
+      </c>
+      <c r="B203">
+        <v>205.3</v>
+      </c>
+      <c r="C203" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D203" s="20">
+        <v>8</v>
+      </c>
+      <c r="E203" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F203">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G203" s="22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="25">
+      <c r="A204" s="1">
+        <v>42057</v>
+      </c>
+      <c r="B204">
+        <v>189</v>
+      </c>
+      <c r="C204" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D204" s="20">
+        <v>8</v>
+      </c>
+      <c r="E204" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F204">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="G204" s="22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="25">
+      <c r="A205" s="1">
+        <v>42058</v>
+      </c>
+      <c r="B205">
+        <v>200.7</v>
+      </c>
+      <c r="C205" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D205" s="20">
+        <v>0</v>
+      </c>
+      <c r="E205" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F205">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="G205" s="22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="25">
+      <c r="A206" s="1">
+        <v>42058</v>
+      </c>
+      <c r="B206">
+        <v>200.7</v>
+      </c>
+      <c r="C206" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D206" s="20">
+        <v>8</v>
+      </c>
+      <c r="E206" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F206">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="G206" s="22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="25">
+      <c r="A207" s="1">
+        <v>42058</v>
+      </c>
+      <c r="B207">
+        <v>158.1</v>
+      </c>
+      <c r="C207" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D207" s="20">
+        <v>8</v>
+      </c>
+      <c r="E207" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F207">
+        <f t="shared" si="5"/>
+        <v>160</v>
+      </c>
+      <c r="G207" s="22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="25">
+      <c r="A208" s="1">
+        <v>42058</v>
+      </c>
+      <c r="B208">
+        <v>212.7</v>
+      </c>
+      <c r="C208" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D208" s="20">
+        <v>8</v>
+      </c>
+      <c r="E208" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F208">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G208" s="22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="25">
+      <c r="A209" s="1">
+        <v>42059</v>
+      </c>
+      <c r="B209">
+        <v>218.3</v>
+      </c>
+      <c r="C209" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D209" s="20">
+        <v>0</v>
+      </c>
+      <c r="E209" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F209">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G209" s="22" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="25">
+      <c r="A210" s="1">
+        <v>42059</v>
+      </c>
+      <c r="B210">
+        <v>231.9</v>
+      </c>
+      <c r="C210" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D210" s="20">
+        <v>8</v>
+      </c>
+      <c r="E210" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F210">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G210" s="22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="25">
+      <c r="A211" s="1">
+        <v>42059</v>
+      </c>
+      <c r="B211">
+        <v>246.3</v>
+      </c>
+      <c r="C211" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D211" s="20">
+        <v>8</v>
+      </c>
+      <c r="E211" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F211">
+        <f t="shared" si="5"/>
+        <v>250</v>
+      </c>
+      <c r="G211" s="22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" ht="25">
+      <c r="A212" s="1">
+        <v>42059</v>
+      </c>
+      <c r="B212">
+        <v>218.5</v>
+      </c>
+      <c r="C212" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D212" s="20">
+        <v>8</v>
+      </c>
+      <c r="E212" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F212">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G212" s="22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="25">
+      <c r="A213" s="1">
+        <v>42060</v>
+      </c>
+      <c r="B213">
+        <v>221</v>
+      </c>
+      <c r="C213" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D213" s="20">
+        <v>0</v>
+      </c>
+      <c r="E213" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F213">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G213" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="25">
+      <c r="A214" s="1">
+        <v>42060</v>
+      </c>
+      <c r="B214">
+        <v>188</v>
+      </c>
+      <c r="C214" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D214" s="20">
+        <v>8</v>
+      </c>
+      <c r="E214" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F214">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="G214" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="25">
+      <c r="A215" s="1">
+        <v>42060</v>
+      </c>
+      <c r="B215">
+        <v>209.1</v>
+      </c>
+      <c r="C215" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D215" s="20">
+        <v>8</v>
+      </c>
+      <c r="E215" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F215">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G215" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="25">
+      <c r="A216" s="1">
+        <v>42060</v>
+      </c>
+      <c r="B216">
+        <v>192</v>
+      </c>
+      <c r="C216" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D216" s="20">
+        <v>8</v>
+      </c>
+      <c r="E216" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F216">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="G216" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="25">
+      <c r="A217" s="1">
+        <v>42062</v>
+      </c>
+      <c r="B217">
+        <v>171.4</v>
+      </c>
+      <c r="C217" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D217" s="20">
+        <v>0</v>
+      </c>
+      <c r="E217" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F217">
+        <f t="shared" si="5"/>
+        <v>170</v>
+      </c>
+      <c r="G217" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="25">
+      <c r="A218" s="1">
+        <v>42062</v>
+      </c>
+      <c r="B218">
+        <v>171.4</v>
+      </c>
+      <c r="C218" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D218" s="20">
+        <v>8</v>
+      </c>
+      <c r="E218" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F218">
+        <f t="shared" si="5"/>
+        <v>170</v>
+      </c>
+      <c r="G218" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="25">
+      <c r="A219" s="1">
+        <v>42062</v>
+      </c>
+      <c r="B219">
+        <v>174.2</v>
+      </c>
+      <c r="C219" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D219" s="20">
+        <v>8</v>
+      </c>
+      <c r="E219" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F219">
+        <f t="shared" si="5"/>
+        <v>170</v>
+      </c>
+      <c r="G219" s="22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="25">
+      <c r="A220" s="1">
+        <v>42062</v>
+      </c>
+      <c r="B220">
+        <v>184.7</v>
+      </c>
+      <c r="C220" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D220" s="20">
+        <v>8</v>
+      </c>
+      <c r="E220" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F220">
+        <f t="shared" si="5"/>
+        <v>180</v>
+      </c>
+      <c r="G220" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="25">
+      <c r="A221" s="1">
+        <v>42063</v>
+      </c>
+      <c r="B221">
+        <v>228.1</v>
+      </c>
+      <c r="C221" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D221" s="20">
+        <v>0</v>
+      </c>
+      <c r="E221" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F221">
+        <f t="shared" si="5"/>
+        <v>230</v>
+      </c>
+      <c r="G221" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="25">
+      <c r="A222" s="1">
+        <v>42063</v>
+      </c>
+      <c r="B222">
+        <v>206.5</v>
+      </c>
+      <c r="C222" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D222" s="20">
+        <v>8</v>
+      </c>
+      <c r="E222" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F222">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G222" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="25">
+      <c r="A223" s="1">
+        <v>42063</v>
+      </c>
+      <c r="B223">
+        <v>221.9</v>
+      </c>
+      <c r="C223" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D223" s="20">
+        <v>8</v>
+      </c>
+      <c r="E223" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F223">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G223" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="25">
+      <c r="A224" s="1">
+        <v>42063</v>
+      </c>
+      <c r="B224">
+        <v>221.9</v>
+      </c>
+      <c r="C224" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D224" s="20">
+        <v>8</v>
+      </c>
+      <c r="E224" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F224">
+        <f t="shared" si="5"/>
+        <v>220</v>
+      </c>
+      <c r="G224" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="25">
+      <c r="A225" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B225">
+        <v>235.7</v>
+      </c>
+      <c r="C225" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D225" s="20">
+        <v>0</v>
+      </c>
+      <c r="E225" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F225">
+        <f t="shared" si="5"/>
+        <v>240</v>
+      </c>
+      <c r="G225" s="22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="25">
+      <c r="A226" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B226">
+        <v>205.8</v>
+      </c>
+      <c r="C226" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D226" s="20">
+        <v>8</v>
+      </c>
+      <c r="E226" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F226">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G226" s="22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="25">
+      <c r="A227" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B227">
+        <v>257.2</v>
+      </c>
+      <c r="C227" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D227" s="20">
+        <v>8</v>
+      </c>
+      <c r="E227" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F227">
+        <f t="shared" si="5"/>
+        <v>260</v>
+      </c>
+      <c r="G227" s="22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="25">
+      <c r="A228" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B228">
+        <v>206</v>
+      </c>
+      <c r="C228" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D228" s="20">
+        <v>8</v>
+      </c>
+      <c r="E228" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F228">
+        <f t="shared" si="5"/>
+        <v>210</v>
+      </c>
+      <c r="G228" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="25">
+      <c r="A229" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B229">
+        <v>202.2</v>
+      </c>
+      <c r="C229" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D229" s="20">
+        <v>0</v>
+      </c>
+      <c r="E229" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F229">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="G229" s="22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="25">
+      <c r="A230" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B230">
+        <v>202.2</v>
+      </c>
+      <c r="C230" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D230" s="20">
+        <v>8</v>
+      </c>
+      <c r="E230" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F230">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="G230" s="22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="25">
+      <c r="A231" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B231">
+        <v>185.9</v>
+      </c>
+      <c r="C231" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D231" s="20">
+        <v>8</v>
+      </c>
+      <c r="E231" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F231">
+        <f t="shared" si="5"/>
+        <v>190</v>
+      </c>
+      <c r="G231" s="22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="25">
+      <c r="A232" s="1">
+        <v>42064</v>
+      </c>
+      <c r="B232">
+        <v>202.2</v>
+      </c>
+      <c r="C232" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D232" s="20">
+        <v>8</v>
+      </c>
+      <c r="E232" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F232">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="G232" s="22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="25">
+      <c r="A233" s="23">
+        <v>42065</v>
+      </c>
+      <c r="B233">
+        <v>202.1</v>
+      </c>
+      <c r="C233" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D233" s="20">
+        <v>0</v>
+      </c>
+      <c r="E233" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F233">
+        <f t="shared" si="5"/>
+        <v>200</v>
+      </c>
+      <c r="G233" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="25">
+      <c r="A234" s="1">
+        <v>42065</v>
+      </c>
+      <c r="B234">
+        <v>202.1</v>
+      </c>
+      <c r="C234" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D234" s="20">
+        <v>8</v>
+      </c>
+      <c r="E234" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F234">
+        <f t="shared" ref="F234:F236" si="6">ROUND(B234/10,0)*10</f>
+        <v>200</v>
+      </c>
+      <c r="G234" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="25">
+      <c r="A235" s="1">
+        <v>42065</v>
+      </c>
+      <c r="B235">
+        <v>197.4</v>
+      </c>
+      <c r="C235" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D235" s="20">
+        <v>8</v>
+      </c>
+      <c r="E235" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F235">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="G235" s="22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="25">
+      <c r="A236" s="1">
+        <v>42065</v>
+      </c>
+      <c r="B236">
+        <v>202.1</v>
+      </c>
+      <c r="C236" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D236" s="20">
+        <v>8</v>
+      </c>
+      <c r="E236" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F236">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="G236" s="22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="25">
+      <c r="A237" s="1">
+        <v>42066</v>
+      </c>
+      <c r="C237" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D237" s="20">
+        <v>0</v>
+      </c>
+      <c r="E237" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G237" s="22" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="25">
+      <c r="A238" s="1">
+        <v>42066</v>
+      </c>
+      <c r="C238" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D238" s="20">
+        <v>8</v>
+      </c>
+      <c r="E238" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G238" s="22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="25">
+      <c r="A239" s="1">
+        <v>42066</v>
+      </c>
+      <c r="C239" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D239" s="20">
+        <v>8</v>
+      </c>
+      <c r="E239" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G239" s="22" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="25">
+      <c r="A240" s="1">
+        <v>42066</v>
+      </c>
+      <c r="C240" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D240" s="20">
+        <v>8</v>
+      </c>
+      <c r="E240" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G240" s="22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="25">
+      <c r="A241" s="1">
+        <v>42067</v>
+      </c>
+      <c r="C241" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D241" s="20">
+        <v>0</v>
+      </c>
+      <c r="E241" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G241" s="22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="25">
+      <c r="A242" s="1">
+        <v>42067</v>
+      </c>
+      <c r="C242" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D242" s="20">
+        <v>8</v>
+      </c>
+      <c r="E242" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G242" s="22" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="25">
+      <c r="A243" s="1">
+        <v>42067</v>
+      </c>
+      <c r="C243" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D243" s="20">
+        <v>8</v>
+      </c>
+      <c r="E243" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G243" s="22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="25">
+      <c r="A244" s="1">
+        <v>42067</v>
+      </c>
+      <c r="C244" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D244" s="20">
+        <v>8</v>
+      </c>
+      <c r="E244" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G244" s="22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1048576" spans="1:1">
+      <c r="A1048576" s="1"/>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G212" r:id="rId1"/>
+    <hyperlink ref="G223" r:id="rId2"/>
+    <hyperlink ref="G224" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="25317"/>
   <workbookPr showInkAnnotation="0" hidePivotFieldList="1" autoCompressPictures="0"/>
   <bookViews>
     <workbookView xWindow="460" yWindow="0" windowWidth="23920" windowHeight="13860" tabRatio="500" activeTab="2"/>
@@ -13,7 +13,7 @@
   </sheets>
   <calcPr calcId="140000" concurrentCalc="0"/>
   <pivotCaches>
-    <pivotCache cacheId="61" r:id="rId4"/>
+    <pivotCache cacheId="32" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="844" uniqueCount="197">
   <si>
     <t>Date</t>
   </si>
@@ -468,6 +468,153 @@
   </si>
   <si>
     <t>S143909636</t>
+  </si>
+  <si>
+    <t>S144502522</t>
+  </si>
+  <si>
+    <t>S144502970</t>
+  </si>
+  <si>
+    <t>S144503377</t>
+  </si>
+  <si>
+    <t>S144503792</t>
+  </si>
+  <si>
+    <t>S145307691</t>
+  </si>
+  <si>
+    <t>S145309035</t>
+  </si>
+  <si>
+    <t>S145310231</t>
+  </si>
+  <si>
+    <t>S145312800</t>
+  </si>
+  <si>
+    <t>S145668333</t>
+  </si>
+  <si>
+    <t>S145670897</t>
+  </si>
+  <si>
+    <t>S145677593</t>
+  </si>
+  <si>
+    <t>S146144981</t>
+  </si>
+  <si>
+    <t>S146145530</t>
+  </si>
+  <si>
+    <t>S146145946</t>
+  </si>
+  <si>
+    <t>S146146507</t>
+  </si>
+  <si>
+    <t>S147006330</t>
+  </si>
+  <si>
+    <t>S147007175</t>
+  </si>
+  <si>
+    <t>S147591151</t>
+  </si>
+  <si>
+    <t>S147591920</t>
+  </si>
+  <si>
+    <t>S147592464</t>
+  </si>
+  <si>
+    <t>S147739477</t>
+  </si>
+  <si>
+    <t>S147739860</t>
+  </si>
+  <si>
+    <t>S147740849</t>
+  </si>
+  <si>
+    <t>S147741172</t>
+  </si>
+  <si>
+    <t>S148302850</t>
+  </si>
+  <si>
+    <t>S148304371</t>
+  </si>
+  <si>
+    <t>S148304791</t>
+  </si>
+  <si>
+    <t>S148305532</t>
+  </si>
+  <si>
+    <t>S148838554</t>
+  </si>
+  <si>
+    <t>S148838891</t>
+  </si>
+  <si>
+    <t>S148839446</t>
+  </si>
+  <si>
+    <t>S148839811</t>
+  </si>
+  <si>
+    <t>S148845427</t>
+  </si>
+  <si>
+    <t>S148846334</t>
+  </si>
+  <si>
+    <t>S148846841</t>
+  </si>
+  <si>
+    <t>S148847165</t>
+  </si>
+  <si>
+    <t>S149435231</t>
+  </si>
+  <si>
+    <t>S149436886</t>
+  </si>
+  <si>
+    <t>S149437418</t>
+  </si>
+  <si>
+    <t>S149438013</t>
+  </si>
+  <si>
+    <t>S149443933</t>
+  </si>
+  <si>
+    <t>S149446636</t>
+  </si>
+  <si>
+    <t>S150764641</t>
+  </si>
+  <si>
+    <t>S150765074</t>
+  </si>
+  <si>
+    <t>S150765519</t>
+  </si>
+  <si>
+    <t>S151391057</t>
+  </si>
+  <si>
+    <t>S151391637</t>
+  </si>
+  <si>
+    <t>S151391990</t>
+  </si>
+  <si>
+    <t>S151392468</t>
   </si>
 </sst>
 </file>
@@ -480,7 +627,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="128"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -511,7 +658,7 @@
       <name val="Helvetica"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -560,6 +707,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -585,7 +738,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="249">
+  <cellStyleXfs count="278">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -835,8 +988,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
@@ -863,11 +1045,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="249">
+  <cellStyles count="278">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="4" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="6" builtinId="9" hidden="1"/>
@@ -1003,6 +1187,35 @@
     <cellStyle name="Followed Hyperlink" xfId="246" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="247" builtinId="9" hidden="1"/>
     <cellStyle name="Followed Hyperlink" xfId="248" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="249" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="250" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="251" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="252" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="253" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="254" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="255" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="256" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="257" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="258" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="259" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="260" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="261" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="262" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="263" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="264" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="265" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="266" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="267" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="268" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="269" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="270" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="271" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="272" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="273" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="274" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="275" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="276" builtinId="9" hidden="1"/>
+    <cellStyle name="Followed Hyperlink" xfId="277" builtinId="9" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8" hidden="1"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8" hidden="1"/>
@@ -1150,107 +1363,119 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet5!$A$5:$A$19</c:f>
+              <c:f>Sheet5!$A$5:$A$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
+                  <c:v>140.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>150.0</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>160.0</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>170.0</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>180.0</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>190.0</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>200.0</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>210.0</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>220.0</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>230.0</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>240.0</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>250.0</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>260.0</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>270.0</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>280.0</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>290.0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>300.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet5!$B$5:$B$19</c:f>
+              <c:f>Sheet5!$B$5:$B$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>4.0</c:v>
+                  <c:v>1.0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>5.0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14.0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30.0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23.0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>47.0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45.0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>32.0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21.0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>20.0</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>7.0</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>15.0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>12.0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>26.0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>18.0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>41.0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>36.0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>23.0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>18.0</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>17.0</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>10.0</c:v>
-                </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>2.0</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
+                  <c:v>1.0</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>1.0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1266,8 +1491,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="-2112807896"/>
-        <c:axId val="-2112811192"/>
+        <c:axId val="-2121808440"/>
+        <c:axId val="1928925848"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1280,108 +1505,120 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Sheet5!$V$3:$V$17</c:f>
+              <c:f>Sheet5!$V$2:$V$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
+                  <c:v>140.0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>150.0</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>160.0</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>170.0</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>180.0</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>190.0</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>200.0</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>210.0</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>220.0</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>230.0</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>240.0</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>250.0</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>260.0</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>270.0</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>280.0</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>290.0</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>300.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet5!$W$3:$W$17</c:f>
+              <c:f>Sheet5!$W$2:$W$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>0.001232257656464</c:v>
+                  <c:v>0.00058339438387284</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00247717835128003</c:v>
+                  <c:v>0.00126714206746574</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.00442119653601064</c:v>
+                  <c:v>0.0024643087002243</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.00700566168510025</c:v>
+                  <c:v>0.00429112976031693</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.00985565051328814</c:v>
+                  <c:v>0.00669044370155647</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0123097213847046</c:v>
+                  <c:v>0.00933995813733147</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.0136501664233175</c:v>
+                  <c:v>0.0116745910017552</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.0134386135061302</c:v>
+                  <c:v>0.0130660752747666</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.0117462104015132</c:v>
+                  <c:v>0.01309348855536</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.00911523526280455</c:v>
+                  <c:v>0.011748226908323</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.00628007431684782</c:v>
+                  <c:v>0.00943834862913248</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.00384139068094988</c:v>
+                  <c:v>0.00678932252331094</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.00208611847027228</c:v>
+                  <c:v>0.0043728401420888</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.00100581070272385</c:v>
+                  <c:v>0.00252178175415552</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.000430546765929341</c:v>
+                  <c:v>0.00130214135253819</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.000602026349872102</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.000249218114019803</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1398,11 +1635,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="-2112817640"/>
-        <c:axId val="-2112814232"/>
+        <c:axId val="-2117347624"/>
+        <c:axId val="1928660792"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-2112817640"/>
+        <c:axId val="-2117347624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1412,7 +1649,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2112814232"/>
+        <c:crossAx val="1928660792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1420,10 +1657,11 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-2112814232"/>
+        <c:axId val="1928660792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="0.015"/>
+          <c:min val="0.0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1432,15 +1670,15 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2112817640"/>
+        <c:crossAx val="-2117347624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="-2112811192"/>
+        <c:axId val="1928925848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="45.0"/>
+          <c:max val="50.0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -1448,12 +1686,12 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2112807896"/>
+        <c:crossAx val="-2121808440"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="-2112807896"/>
+        <c:axId val="-2121808440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1463,7 +1701,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="-2112811192"/>
+        <c:crossAx val="1928925848"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1523,16 +1761,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Jesse Green" refreshedDate="42066.385978819446" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="235">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Jesse Green" refreshedDate="42079.851732291667" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="290">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:F236" sheet="Sheet4"/>
+    <worksheetSource ref="A1:F291" sheet="Sheet4"/>
   </cacheSource>
   <cacheFields count="6">
     <cacheField name="date" numFmtId="14">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2014-01-25T00:00:00" maxDate="2015-03-03T00:00:00"/>
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2014-01-25T00:00:00" maxDate="2015-03-15T00:00:00"/>
     </cacheField>
     <cacheField name="score" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="150.5" maxValue="291.10000000000002"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="135.4" maxValue="302.3"/>
     </cacheField>
     <cacheField name="model" numFmtId="0">
       <sharedItems/>
@@ -1544,7 +1782,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="rounded" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="150" maxValue="290" count="15">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="130" maxValue="300" count="18">
         <n v="240"/>
         <n v="170"/>
         <n v="220"/>
@@ -1560,6 +1798,9 @@
         <n v="200"/>
         <n v="150"/>
         <n v="290"/>
+        <n v="300"/>
+        <n v="140"/>
+        <n v="130" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -1572,7 +1813,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="235">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="290">
   <r>
     <d v="2015-01-15T00:00:00"/>
     <n v="235.4"/>
@@ -3452,13 +3693,453 @@
     <n v="8"/>
     <s v="l2"/>
     <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-03T00:00:00"/>
+    <n v="182.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-03-03T00:00:00"/>
+    <n v="216.7"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-03T00:00:00"/>
+    <n v="206.5"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-03-03T00:00:00"/>
+    <n v="225"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-04T00:00:00"/>
+    <n v="245.1"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-03-04T00:00:00"/>
+    <n v="274.89999999999998"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-03-04T00:00:00"/>
+    <n v="273.89999999999998"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-03-04T00:00:00"/>
+    <n v="247.8"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-03-05T00:00:00"/>
+    <n v="207.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-03-05T00:00:00"/>
+    <n v="234.1"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-05T00:00:00"/>
+    <n v="218.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-05T00:00:00"/>
+    <n v="219.1"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-07T00:00:00"/>
+    <n v="256"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <d v="2015-03-07T00:00:00"/>
+    <n v="271.2"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-03-07T00:00:00"/>
+    <n v="273.39999999999998"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-03-07T00:00:00"/>
+    <n v="302.3"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="15"/>
+  </r>
+  <r>
+    <d v="2015-03-07T00:00:00"/>
+    <n v="274.3"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-03-07T00:00:00"/>
+    <n v="263.60000000000002"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <d v="2015-03-07T00:00:00"/>
+    <n v="265.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-03-07T00:00:00"/>
+    <n v="274.3"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="11"/>
+  </r>
+  <r>
+    <d v="2015-03-08T00:00:00"/>
+    <n v="217.1"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-08T00:00:00"/>
+    <n v="196"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-08T00:00:00"/>
+    <n v="214"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-03-08T00:00:00"/>
+    <n v="201.4"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-10T00:00:00"/>
+    <n v="237.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-03-10T00:00:00"/>
+    <n v="237.2"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-03-10T00:00:00"/>
+    <n v="216.8"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-10T00:00:00"/>
+    <n v="237.2"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="214.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="225.9"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="234.2"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="225.9"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="245.9"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="225.6"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="199.6"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-11T00:00:00"/>
+    <n v="227.6"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-12T00:00:00"/>
+    <n v="219.2"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-12T00:00:00"/>
+    <n v="221.4"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-12T00:00:00"/>
+    <n v="218.4"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-12T00:00:00"/>
+    <n v="231.3"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-13T00:00:00"/>
+    <n v="203.6"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-13T00:00:00"/>
+    <n v="202.2"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="12"/>
+  </r>
+  <r>
+    <d v="2015-03-13T00:00:00"/>
+    <n v="186.6"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-03-13T00:00:00"/>
+    <n v="180.9"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="10"/>
+  </r>
+  <r>
+    <d v="2015-03-13T00:00:00"/>
+    <n v="206.6"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-03-13T00:00:00"/>
+    <n v="219.8"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <d v="2015-03-13T00:00:00"/>
+    <n v="212.9"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <d v="2015-03-13T00:00:00"/>
+    <n v="230.1"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <d v="2015-03-14T00:00:00"/>
+    <n v="135.4"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="16"/>
+  </r>
+  <r>
+    <d v="2015-03-14T00:00:00"/>
+    <n v="148.19999999999999"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="13"/>
+  </r>
+  <r>
+    <d v="2015-03-14T00:00:00"/>
+    <n v="167.2"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <d v="2015-03-14T00:00:00"/>
+    <n v="157.1"/>
+    <s v="NN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="9"/>
+  </r>
+  <r>
+    <d v="2015-03-14T00:00:00"/>
+    <n v="186.3"/>
+    <s v="EN"/>
+    <n v="0"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-03-14T00:00:00"/>
+    <n v="186.3"/>
+    <s v="EN"/>
+    <n v="8"/>
+    <s v="l2"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <d v="2015-03-14T00:00:00"/>
+    <n v="186.3"/>
+    <s v="SVR"/>
+    <n v="8"/>
+    <s v="l1"/>
+    <x v="7"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="61" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
-  <location ref="A3:B20" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="32" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
+  <location ref="A3:B22" firstHeaderRow="2" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -3466,7 +4147,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
-      <items count="16">
+      <items count="19">
+        <item x="16"/>
         <item x="13"/>
         <item x="9"/>
         <item x="1"/>
@@ -3482,6 +4164,8 @@
         <item x="11"/>
         <item x="8"/>
         <item x="14"/>
+        <item x="15"/>
+        <item m="1" x="17"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -3489,7 +4173,7 @@
   <rowFields count="1">
     <field x="5"/>
   </rowFields>
-  <rowItems count="16">
+  <rowItems count="18">
     <i>
       <x/>
     </i>
@@ -3534,6 +4218,12 @@
     </i>
     <i>
       <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
     </i>
     <i t="grand">
       <x/>
@@ -3884,26 +4574,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="53" customHeight="1">
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24" t="s">
+      <c r="C1" s="25"/>
+      <c r="D1" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24" t="s">
+      <c r="E1" s="25"/>
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24" t="s">
+      <c r="G1" s="25"/>
+      <c r="H1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24" t="s">
+      <c r="I1" s="25"/>
+      <c r="J1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="24"/>
+      <c r="K1" s="25"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" t="s">
@@ -4587,7 +5277,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:W20"/>
+  <dimension ref="A2:W22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="13.1640625" customWidth="1"/>
@@ -4599,6 +5289,15 @@
     <col min="13" max="15" width="6.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="1:23">
+      <c r="V2">
+        <v>140</v>
+      </c>
+      <c r="W2">
+        <f>_xlfn.NORM.DIST(V2,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>5.833943838728403E-4</v>
+      </c>
+    </row>
     <row r="3" spans="1:23">
       <c r="A3" s="16" t="s">
         <v>21</v>
@@ -4608,7 +5307,7 @@
       </c>
       <c r="W3">
         <f>_xlfn.NORM.DIST(V3,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.2322576564640026E-3</v>
+        <v>1.2671420674657372E-3</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -4623,229 +5322,255 @@
       </c>
       <c r="W4">
         <f>_xlfn.NORM.DIST(V4,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>2.4771783512800303E-3</v>
+        <v>2.464308700224304E-3</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="17">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B5" s="18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V5">
         <v>170</v>
       </c>
       <c r="W5">
         <f>_xlfn.NORM.DIST(V5,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>4.4211965360106409E-3</v>
+        <v>4.2911297603169269E-3</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="17">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B6" s="18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>180</v>
       </c>
       <c r="W6">
         <f>_xlfn.NORM.DIST(V6,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>7.0056616851002533E-3</v>
+        <v>6.6904437015564699E-3</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="17">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B7" s="18">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>190</v>
       </c>
       <c r="W7">
         <f>_xlfn.NORM.DIST(V7,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>9.8556505132881399E-3</v>
+        <v>9.339958137331475E-3</v>
       </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="17">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B8" s="18">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V8">
         <v>200</v>
       </c>
       <c r="W8">
         <f>_xlfn.NORM.DIST(V8,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.2309721384704569E-2</v>
+        <v>1.1674591001755195E-2</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="17">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B9" s="18">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="V9">
         <v>210</v>
       </c>
       <c r="W9">
         <f>_xlfn.NORM.DIST(V9,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.3650166423317553E-2</v>
+        <v>1.3066075274766623E-2</v>
       </c>
     </row>
     <row r="10" spans="1:23">
       <c r="A10" s="17">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B10" s="18">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="V10">
         <v>220</v>
       </c>
       <c r="W10">
         <f>_xlfn.NORM.DIST(V10,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.3438613506130237E-2</v>
+        <v>1.3093488555359975E-2</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="17">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="B11" s="18">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="V11">
         <v>230</v>
       </c>
       <c r="W11">
         <f>_xlfn.NORM.DIST(V11,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.1746210401513217E-2</v>
+        <v>1.174822690832303E-2</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="17">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B12" s="18">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="V12">
         <v>240</v>
       </c>
       <c r="W12">
         <f>_xlfn.NORM.DIST(V12,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>9.1152352628045517E-3</v>
+        <v>9.4383486291324814E-3</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" s="17">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B13" s="18">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="V13">
         <v>250</v>
       </c>
       <c r="W13">
         <f>_xlfn.NORM.DIST(V13,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>6.2800743168478241E-3</v>
+        <v>6.7893225233109453E-3</v>
       </c>
     </row>
     <row r="14" spans="1:23">
       <c r="A14" s="17">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B14" s="18">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="V14">
         <v>260</v>
       </c>
       <c r="W14">
         <f>_xlfn.NORM.DIST(V14,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>3.8413906809498812E-3</v>
+        <v>4.3728401420888028E-3</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" s="17">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B15" s="18">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V15">
         <v>270</v>
       </c>
       <c r="W15">
         <f>_xlfn.NORM.DIST(V15,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>2.0861184702722761E-3</v>
+        <v>2.5217817541555222E-3</v>
       </c>
     </row>
     <row r="16" spans="1:23">
       <c r="A16" s="17">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B16" s="18">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="V16">
         <v>280</v>
       </c>
       <c r="W16">
         <f>_xlfn.NORM.DIST(V16,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>1.0058107027238546E-3</v>
+        <v>1.3021413525381874E-3</v>
       </c>
     </row>
     <row r="17" spans="1:23">
       <c r="A17" s="17">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B17" s="18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>290</v>
       </c>
       <c r="W17">
         <f>_xlfn.NORM.DIST(V17,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
-        <v>4.3054676592934135E-4</v>
+        <v>6.0202634987210196E-4</v>
       </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="17">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B18" s="18">
-        <v>2</v>
+        <v>17</v>
+      </c>
+      <c r="V18">
+        <v>300</v>
+      </c>
+      <c r="W18">
+        <f>_xlfn.NORM.DIST(V18,Sheet4!$J$2,Sheet4!$J$3,FALSE)</f>
+        <v>2.4921811401980315E-4</v>
       </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="17">
+        <v>280</v>
+      </c>
+      <c r="B19" s="18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" s="17">
         <v>290</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B20" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
-      <c r="A20" s="17" t="s">
+    <row r="21" spans="1:23">
+      <c r="A21" s="17">
+        <v>300</v>
+      </c>
+      <c r="B21" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="18">
-        <v>235</v>
+      <c r="B22" s="18">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A3:B22">
+    <sortCondition ref="A12"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId2"/>
   <extLst>
@@ -4913,7 +5638,7 @@
       </c>
       <c r="J2">
         <f>AVERAGE(B:B)</f>
-        <v>213.68723404255331</v>
+        <v>215.18965517241392</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="18">
@@ -4941,7 +5666,7 @@
       </c>
       <c r="J3">
         <f>_xlfn.STDEV.S(B:B)</f>
-        <v>28.99075019756452</v>
+        <v>30.081674804608173</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="18">
@@ -10838,7 +11563,7 @@
         <v>13</v>
       </c>
       <c r="F234">
-        <f t="shared" ref="F234:F236" si="6">ROUND(B234/10,0)*10</f>
+        <f t="shared" ref="F234:F291" si="6">ROUND(B234/10,0)*10</f>
         <v>200</v>
       </c>
       <c r="G234" s="22" t="s">
@@ -10897,6 +11622,9 @@
       <c r="A237" s="1">
         <v>42066</v>
       </c>
+      <c r="B237">
+        <v>182.4</v>
+      </c>
       <c r="C237" s="20" t="s">
         <v>12</v>
       </c>
@@ -10905,6 +11633,10 @@
       </c>
       <c r="E237" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F237">
+        <f t="shared" si="6"/>
+        <v>180</v>
       </c>
       <c r="G237" s="22" t="s">
         <v>140</v>
@@ -10914,6 +11646,9 @@
       <c r="A238" s="1">
         <v>42066</v>
       </c>
+      <c r="B238">
+        <v>216.7</v>
+      </c>
       <c r="C238" s="20" t="s">
         <v>12</v>
       </c>
@@ -10922,6 +11657,10 @@
       </c>
       <c r="E238" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F238">
+        <f t="shared" si="6"/>
+        <v>220</v>
       </c>
       <c r="G238" s="22" t="s">
         <v>141</v>
@@ -10931,6 +11670,9 @@
       <c r="A239" s="1">
         <v>42066</v>
       </c>
+      <c r="B239">
+        <v>206.5</v>
+      </c>
       <c r="C239" s="20" t="s">
         <v>20</v>
       </c>
@@ -10939,6 +11681,10 @@
       </c>
       <c r="E239" s="19" t="s">
         <v>19</v>
+      </c>
+      <c r="F239">
+        <f t="shared" si="6"/>
+        <v>210</v>
       </c>
       <c r="G239" s="22" t="s">
         <v>142</v>
@@ -10948,6 +11694,9 @@
       <c r="A240" s="1">
         <v>42066</v>
       </c>
+      <c r="B240">
+        <v>225</v>
+      </c>
       <c r="C240" s="20" t="s">
         <v>56</v>
       </c>
@@ -10956,6 +11705,10 @@
       </c>
       <c r="E240" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F240">
+        <f t="shared" si="6"/>
+        <v>230</v>
       </c>
       <c r="G240" s="22" t="s">
         <v>143</v>
@@ -10965,6 +11718,9 @@
       <c r="A241" s="1">
         <v>42067</v>
       </c>
+      <c r="B241">
+        <v>245.1</v>
+      </c>
       <c r="C241" s="20" t="s">
         <v>12</v>
       </c>
@@ -10973,6 +11729,10 @@
       </c>
       <c r="E241" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F241">
+        <f t="shared" si="6"/>
+        <v>250</v>
       </c>
       <c r="G241" s="22" t="s">
         <v>144</v>
@@ -10982,6 +11742,9 @@
       <c r="A242" s="1">
         <v>42067</v>
       </c>
+      <c r="B242">
+        <v>274.89999999999998</v>
+      </c>
       <c r="C242" s="20" t="s">
         <v>12</v>
       </c>
@@ -10990,6 +11753,10 @@
       </c>
       <c r="E242" s="19" t="s">
         <v>13</v>
+      </c>
+      <c r="F242">
+        <f t="shared" si="6"/>
+        <v>270</v>
       </c>
       <c r="G242" s="22" t="s">
         <v>145</v>
@@ -10999,6 +11766,9 @@
       <c r="A243" s="1">
         <v>42067</v>
       </c>
+      <c r="B243">
+        <v>273.89999999999998</v>
+      </c>
       <c r="C243" s="20" t="s">
         <v>20</v>
       </c>
@@ -11007,6 +11777,10 @@
       </c>
       <c r="E243" s="19" t="s">
         <v>19</v>
+      </c>
+      <c r="F243">
+        <f t="shared" si="6"/>
+        <v>270</v>
       </c>
       <c r="G243" s="22" t="s">
         <v>146</v>
@@ -11016,6 +11790,9 @@
       <c r="A244" s="1">
         <v>42067</v>
       </c>
+      <c r="B244">
+        <v>247.8</v>
+      </c>
       <c r="C244" s="20" t="s">
         <v>56</v>
       </c>
@@ -11025,8 +11802,1293 @@
       <c r="E244" s="19" t="s">
         <v>13</v>
       </c>
+      <c r="F244">
+        <f t="shared" si="6"/>
+        <v>250</v>
+      </c>
       <c r="G244" s="22" t="s">
         <v>147</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="25">
+      <c r="A245" s="1">
+        <v>42068</v>
+      </c>
+      <c r="B245">
+        <v>207.9</v>
+      </c>
+      <c r="C245" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D245" s="20">
+        <v>0</v>
+      </c>
+      <c r="E245" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F245">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="G245" s="22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" ht="25">
+      <c r="A246" s="1">
+        <v>42068</v>
+      </c>
+      <c r="B246">
+        <v>234.1</v>
+      </c>
+      <c r="C246" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D246" s="20">
+        <v>8</v>
+      </c>
+      <c r="E246" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F246">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="G246" s="22" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="25">
+      <c r="A247" s="1">
+        <v>42068</v>
+      </c>
+      <c r="B247">
+        <v>218.9</v>
+      </c>
+      <c r="C247" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D247" s="20">
+        <v>8</v>
+      </c>
+      <c r="E247" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F247">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="G247" s="22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="25">
+      <c r="A248" s="1">
+        <v>42068</v>
+      </c>
+      <c r="B248">
+        <v>219.1</v>
+      </c>
+      <c r="C248" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D248" s="20">
+        <v>8</v>
+      </c>
+      <c r="E248" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F248">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="G248" s="22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="25">
+      <c r="A249" s="1">
+        <v>42070</v>
+      </c>
+      <c r="B249">
+        <v>256</v>
+      </c>
+      <c r="C249" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D249" s="20">
+        <v>0</v>
+      </c>
+      <c r="E249" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F249">
+        <f t="shared" si="6"/>
+        <v>260</v>
+      </c>
+      <c r="G249" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="25">
+      <c r="A250" s="1">
+        <v>42070</v>
+      </c>
+      <c r="B250">
+        <v>271.2</v>
+      </c>
+      <c r="C250" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D250" s="20">
+        <v>8</v>
+      </c>
+      <c r="E250" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F250">
+        <f t="shared" si="6"/>
+        <v>270</v>
+      </c>
+      <c r="G250" s="22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="25">
+      <c r="A251" s="1">
+        <v>42070</v>
+      </c>
+      <c r="B251">
+        <v>273.39999999999998</v>
+      </c>
+      <c r="C251" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D251" s="20">
+        <v>8</v>
+      </c>
+      <c r="E251" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F251">
+        <f t="shared" si="6"/>
+        <v>270</v>
+      </c>
+      <c r="G251" s="22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" ht="25">
+      <c r="A252" s="1">
+        <v>42070</v>
+      </c>
+      <c r="B252">
+        <v>302.3</v>
+      </c>
+      <c r="C252" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D252" s="20">
+        <v>8</v>
+      </c>
+      <c r="E252" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F252">
+        <f t="shared" si="6"/>
+        <v>300</v>
+      </c>
+      <c r="G252" s="22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="25">
+      <c r="A253" s="1">
+        <v>42070</v>
+      </c>
+      <c r="B253">
+        <v>274.3</v>
+      </c>
+      <c r="C253" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D253" s="20">
+        <v>0</v>
+      </c>
+      <c r="E253" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F253">
+        <f t="shared" si="6"/>
+        <v>270</v>
+      </c>
+      <c r="G253" s="22" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" ht="25">
+      <c r="A254" s="1">
+        <v>42070</v>
+      </c>
+      <c r="B254">
+        <v>263.60000000000002</v>
+      </c>
+      <c r="C254" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D254" s="20">
+        <v>8</v>
+      </c>
+      <c r="E254" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F254">
+        <f t="shared" si="6"/>
+        <v>260</v>
+      </c>
+      <c r="G254" s="22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="25">
+      <c r="A255" s="1">
+        <v>42070</v>
+      </c>
+      <c r="B255">
+        <v>265.3</v>
+      </c>
+      <c r="C255" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D255" s="20">
+        <v>8</v>
+      </c>
+      <c r="E255" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F255">
+        <f t="shared" si="6"/>
+        <v>270</v>
+      </c>
+      <c r="G255" s="22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="25">
+      <c r="A256" s="1">
+        <v>42070</v>
+      </c>
+      <c r="B256">
+        <v>274.3</v>
+      </c>
+      <c r="C256" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D256" s="20">
+        <v>8</v>
+      </c>
+      <c r="E256" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F256">
+        <f t="shared" si="6"/>
+        <v>270</v>
+      </c>
+      <c r="G256" s="22" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" ht="25">
+      <c r="A257" s="1">
+        <v>42071</v>
+      </c>
+      <c r="B257">
+        <v>217.1</v>
+      </c>
+      <c r="C257" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D257" s="20">
+        <v>0</v>
+      </c>
+      <c r="E257" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F257">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="G257" s="22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" ht="25">
+      <c r="A258" s="1">
+        <v>42071</v>
+      </c>
+      <c r="B258">
+        <v>196</v>
+      </c>
+      <c r="C258" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D258" s="20">
+        <v>8</v>
+      </c>
+      <c r="E258" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F258">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="G258" s="22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="25">
+      <c r="A259" s="1">
+        <v>42071</v>
+      </c>
+      <c r="B259">
+        <v>214</v>
+      </c>
+      <c r="C259" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D259" s="20">
+        <v>8</v>
+      </c>
+      <c r="E259" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F259">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="G259" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="25">
+      <c r="A260" s="1">
+        <v>42071</v>
+      </c>
+      <c r="B260">
+        <v>201.4</v>
+      </c>
+      <c r="C260" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D260" s="20">
+        <v>8</v>
+      </c>
+      <c r="E260" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F260">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="G260" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" ht="25">
+      <c r="A261" s="1">
+        <v>42073</v>
+      </c>
+      <c r="B261">
+        <v>237.2</v>
+      </c>
+      <c r="C261" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D261" s="20">
+        <v>0</v>
+      </c>
+      <c r="E261" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F261">
+        <f t="shared" si="6"/>
+        <v>240</v>
+      </c>
+      <c r="G261" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" ht="25">
+      <c r="A262" s="1">
+        <v>42073</v>
+      </c>
+      <c r="B262">
+        <v>237.2</v>
+      </c>
+      <c r="C262" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D262" s="20">
+        <v>8</v>
+      </c>
+      <c r="E262" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F262">
+        <f t="shared" si="6"/>
+        <v>240</v>
+      </c>
+      <c r="G262" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" ht="25">
+      <c r="A263" s="1">
+        <v>42073</v>
+      </c>
+      <c r="B263">
+        <v>216.8</v>
+      </c>
+      <c r="C263" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D263" s="20">
+        <v>8</v>
+      </c>
+      <c r="E263" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F263">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="G263" s="22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" ht="25">
+      <c r="A264" s="1">
+        <v>42073</v>
+      </c>
+      <c r="B264">
+        <v>237.2</v>
+      </c>
+      <c r="C264" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D264" s="20">
+        <v>8</v>
+      </c>
+      <c r="E264" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F264">
+        <f t="shared" si="6"/>
+        <v>240</v>
+      </c>
+      <c r="G264" s="22" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" ht="25">
+      <c r="A265" s="1">
+        <v>42074</v>
+      </c>
+      <c r="B265">
+        <v>214.4</v>
+      </c>
+      <c r="C265" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D265" s="20">
+        <v>0</v>
+      </c>
+      <c r="E265" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F265">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="G265" s="22" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" ht="25">
+      <c r="A266" s="1">
+        <v>42074</v>
+      </c>
+      <c r="B266">
+        <v>225.9</v>
+      </c>
+      <c r="C266" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D266" s="20">
+        <v>8</v>
+      </c>
+      <c r="E266" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F266">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="G266" s="22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" ht="25">
+      <c r="A267" s="1">
+        <v>42074</v>
+      </c>
+      <c r="B267">
+        <v>234.2</v>
+      </c>
+      <c r="C267" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D267" s="20">
+        <v>8</v>
+      </c>
+      <c r="E267" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F267">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="G267" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="25">
+      <c r="A268" s="1">
+        <v>42074</v>
+      </c>
+      <c r="B268">
+        <v>225.9</v>
+      </c>
+      <c r="C268" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D268" s="20">
+        <v>8</v>
+      </c>
+      <c r="E268" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F268">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="G268" s="22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" ht="25">
+      <c r="A269" s="1">
+        <v>42074</v>
+      </c>
+      <c r="B269">
+        <v>245.9</v>
+      </c>
+      <c r="C269" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D269" s="20">
+        <v>0</v>
+      </c>
+      <c r="E269" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F269">
+        <f t="shared" si="6"/>
+        <v>250</v>
+      </c>
+      <c r="G269" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" ht="25">
+      <c r="A270" s="1">
+        <v>42074</v>
+      </c>
+      <c r="B270">
+        <v>225.6</v>
+      </c>
+      <c r="C270" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D270" s="20">
+        <v>8</v>
+      </c>
+      <c r="E270" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F270">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="G270" s="22" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" ht="25">
+      <c r="A271" s="1">
+        <v>42074</v>
+      </c>
+      <c r="B271">
+        <v>199.6</v>
+      </c>
+      <c r="C271" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D271" s="20">
+        <v>8</v>
+      </c>
+      <c r="E271" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F271">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="G271" s="22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" ht="25">
+      <c r="A272" s="1">
+        <v>42074</v>
+      </c>
+      <c r="B272">
+        <v>227.6</v>
+      </c>
+      <c r="C272" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D272" s="20">
+        <v>8</v>
+      </c>
+      <c r="E272" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F272">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="G272" s="22" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" ht="25">
+      <c r="A273" s="1">
+        <v>42075</v>
+      </c>
+      <c r="B273">
+        <v>219.2</v>
+      </c>
+      <c r="C273" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D273" s="20">
+        <v>0</v>
+      </c>
+      <c r="E273" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F273">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="G273" s="22" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="25">
+      <c r="A274" s="1">
+        <v>42075</v>
+      </c>
+      <c r="B274">
+        <v>221.4</v>
+      </c>
+      <c r="C274" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D274" s="20">
+        <v>8</v>
+      </c>
+      <c r="E274" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F274">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="G274" s="22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="25">
+      <c r="A275" s="1">
+        <v>42075</v>
+      </c>
+      <c r="B275">
+        <v>218.4</v>
+      </c>
+      <c r="C275" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D275" s="20">
+        <v>8</v>
+      </c>
+      <c r="E275" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F275">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="G275" s="22" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="25">
+      <c r="A276" s="1">
+        <v>42075</v>
+      </c>
+      <c r="B276">
+        <v>231.3</v>
+      </c>
+      <c r="C276" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D276" s="20">
+        <v>8</v>
+      </c>
+      <c r="E276" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F276">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="G276" s="22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="25">
+      <c r="A277" s="1">
+        <v>42076</v>
+      </c>
+      <c r="B277">
+        <v>203.6</v>
+      </c>
+      <c r="C277" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D277" s="20">
+        <v>0</v>
+      </c>
+      <c r="E277" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F277">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="G277" s="22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" ht="25">
+      <c r="A278" s="1">
+        <v>42076</v>
+      </c>
+      <c r="B278">
+        <v>202.2</v>
+      </c>
+      <c r="C278" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D278" s="20">
+        <v>8</v>
+      </c>
+      <c r="E278" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F278">
+        <f t="shared" si="6"/>
+        <v>200</v>
+      </c>
+      <c r="G278" s="22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="25">
+      <c r="A279" s="1">
+        <v>42076</v>
+      </c>
+      <c r="B279">
+        <v>186.6</v>
+      </c>
+      <c r="C279" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D279" s="20">
+        <v>8</v>
+      </c>
+      <c r="E279" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F279">
+        <f t="shared" si="6"/>
+        <v>190</v>
+      </c>
+      <c r="G279" s="22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="25">
+      <c r="A280" s="1">
+        <v>42076</v>
+      </c>
+      <c r="B280">
+        <v>180.9</v>
+      </c>
+      <c r="C280" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D280" s="20">
+        <v>8</v>
+      </c>
+      <c r="E280" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F280">
+        <f t="shared" si="6"/>
+        <v>180</v>
+      </c>
+      <c r="G280" s="22" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" ht="25">
+      <c r="A281" s="1">
+        <v>42076</v>
+      </c>
+      <c r="B281">
+        <v>206.6</v>
+      </c>
+      <c r="C281" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D281" s="20">
+        <v>0</v>
+      </c>
+      <c r="E281" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F281">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="G281" s="22" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="25">
+      <c r="A282" s="1">
+        <v>42076</v>
+      </c>
+      <c r="B282">
+        <v>219.8</v>
+      </c>
+      <c r="C282" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D282" s="20">
+        <v>8</v>
+      </c>
+      <c r="E282" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F282">
+        <f t="shared" si="6"/>
+        <v>220</v>
+      </c>
+      <c r="G282" s="22" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="25">
+      <c r="A283" s="1">
+        <v>42076</v>
+      </c>
+      <c r="B283">
+        <v>212.9</v>
+      </c>
+      <c r="C283" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D283" s="20">
+        <v>8</v>
+      </c>
+      <c r="E283" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F283">
+        <f t="shared" si="6"/>
+        <v>210</v>
+      </c>
+      <c r="G283" s="22" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="25">
+      <c r="A284" s="1">
+        <v>42076</v>
+      </c>
+      <c r="B284">
+        <v>230.1</v>
+      </c>
+      <c r="C284" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D284" s="20">
+        <v>8</v>
+      </c>
+      <c r="E284" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F284">
+        <f t="shared" si="6"/>
+        <v>230</v>
+      </c>
+      <c r="G284" s="22" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="25">
+      <c r="A285" s="1">
+        <v>42077</v>
+      </c>
+      <c r="B285" s="24">
+        <v>135.4</v>
+      </c>
+      <c r="C285" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D285" s="20">
+        <v>0</v>
+      </c>
+      <c r="E285" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F285">
+        <f t="shared" si="6"/>
+        <v>140</v>
+      </c>
+      <c r="G285" s="22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="25">
+      <c r="A286" s="1">
+        <v>42077</v>
+      </c>
+      <c r="B286">
+        <v>148.19999999999999</v>
+      </c>
+      <c r="C286" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D286" s="20">
+        <v>8</v>
+      </c>
+      <c r="E286" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F286">
+        <f t="shared" si="6"/>
+        <v>150</v>
+      </c>
+      <c r="G286" s="22" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" ht="25">
+      <c r="A287" s="1">
+        <v>42077</v>
+      </c>
+      <c r="B287">
+        <v>167.2</v>
+      </c>
+      <c r="C287" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D287" s="20">
+        <v>8</v>
+      </c>
+      <c r="E287" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F287">
+        <f t="shared" si="6"/>
+        <v>170</v>
+      </c>
+      <c r="G287" s="22" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" ht="25">
+      <c r="A288" s="1">
+        <v>42077</v>
+      </c>
+      <c r="B288">
+        <v>157.1</v>
+      </c>
+      <c r="C288" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D288" s="20">
+        <v>8</v>
+      </c>
+      <c r="E288" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F288">
+        <f t="shared" si="6"/>
+        <v>160</v>
+      </c>
+      <c r="G288" s="22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7" ht="25">
+      <c r="A289" s="1">
+        <v>42077</v>
+      </c>
+      <c r="B289">
+        <v>186.3</v>
+      </c>
+      <c r="C289" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D289" s="20">
+        <v>0</v>
+      </c>
+      <c r="E289" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F289">
+        <f t="shared" si="6"/>
+        <v>190</v>
+      </c>
+      <c r="G289" s="22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" ht="25">
+      <c r="A290" s="1">
+        <v>42077</v>
+      </c>
+      <c r="B290">
+        <v>186.3</v>
+      </c>
+      <c r="C290" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D290" s="20">
+        <v>8</v>
+      </c>
+      <c r="E290" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F290">
+        <f t="shared" si="6"/>
+        <v>190</v>
+      </c>
+      <c r="G290" s="22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" ht="25">
+      <c r="A291" s="1">
+        <v>42077</v>
+      </c>
+      <c r="B291">
+        <v>186.3</v>
+      </c>
+      <c r="C291" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D291" s="20">
+        <v>8</v>
+      </c>
+      <c r="E291" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F291">
+        <f t="shared" si="6"/>
+        <v>190</v>
+      </c>
+      <c r="G291" s="22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="25">
+      <c r="A292" s="1">
+        <v>42077</v>
+      </c>
+      <c r="C292" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D292" s="20">
+        <v>8</v>
+      </c>
+      <c r="E292" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G292" s="22" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="25">
+      <c r="A293" s="1">
+        <v>42080</v>
+      </c>
+      <c r="C293" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D293" s="20">
+        <v>0</v>
+      </c>
+      <c r="E293" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G293" s="22" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="25">
+      <c r="A294" s="1">
+        <v>42080</v>
+      </c>
+      <c r="C294" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D294" s="20">
+        <v>8</v>
+      </c>
+      <c r="E294" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G294" s="22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="25">
+      <c r="A295" s="1">
+        <v>42080</v>
+      </c>
+      <c r="C295" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D295" s="20">
+        <v>8</v>
+      </c>
+      <c r="E295" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G295" s="22" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" ht="25">
+      <c r="A296" s="1">
+        <v>42080</v>
+      </c>
+      <c r="C296" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D296" s="20">
+        <v>8</v>
+      </c>
+      <c r="E296" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G296" s="22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" ht="25">
+      <c r="A297" s="26">
+        <v>42081</v>
+      </c>
+      <c r="C297" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D297" s="20">
+        <v>0</v>
+      </c>
+      <c r="E297" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G297" s="22" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" ht="25">
+      <c r="A298" s="26">
+        <v>42081</v>
+      </c>
+      <c r="C298" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D298" s="20">
+        <v>8</v>
+      </c>
+      <c r="E298" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G298" s="22" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="25">
+      <c r="A299" s="26">
+        <v>42081</v>
+      </c>
+      <c r="C299" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D299" s="20">
+        <v>8</v>
+      </c>
+      <c r="E299" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G299" s="22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="25">
+      <c r="A300" s="26">
+        <v>42081</v>
+      </c>
+      <c r="C300" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D300" s="20">
+        <v>8</v>
+      </c>
+      <c r="E300" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G300" s="22" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="1048576" spans="1:1">
